--- a/Imoveis_consolidado.xlsx
+++ b/Imoveis_consolidado.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consolidado" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LUOS_Vinculacao" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TB55_Observacoes" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TB55_Processos" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TB55_Alienacoes" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leia-me" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Consolidado" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="LUOS_Vinculacao" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="TB55_Observacoes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="TB55_Processos" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="TB55_Alienacoes" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Leia-me" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$CI$126</definedName>
@@ -27,9 +27,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -80,15 +79,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1209,7 +1210,7 @@
           <t>2 OFICIO DE REG DE IMOVEIS</t>
         </is>
       </c>
-      <c r="BB2" s="4" t="n">
+      <c r="BB2" s="6" t="n">
         <v>37664</v>
       </c>
       <c r="BC2" s="2" t="inlineStr">
@@ -1234,7 +1235,7 @@
       <c r="BH2" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="BI2" s="4" t="n">
+      <c r="BI2" s="6" t="n">
         <v>45868.4741087963</v>
       </c>
       <c r="BJ2" s="2" t="inlineStr">
@@ -1245,9 +1246,9 @@
       <c r="BK2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="BL2" s="2" t="inlineStr">
-        <is>
-          <t>7.38820722023807e+18</t>
+      <c r="BL2" s="7" t="inlineStr">
+        <is>
+          <t>07388207220238070001</t>
         </is>
       </c>
       <c r="BM2" s="2" t="inlineStr"/>
@@ -1258,7 +1259,7 @@
       <c r="BP2" s="2" t="n">
         <v>113552</v>
       </c>
-      <c r="BQ2" s="4" t="n">
+      <c r="BQ2" s="6" t="n">
         <v>44683</v>
       </c>
       <c r="BR2" s="2" t="inlineStr">
@@ -1530,7 +1531,7 @@
       <c r="BK3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL3" s="2" t="inlineStr"/>
+      <c r="BL3" s="2" t="n"/>
       <c r="BM3" s="2" t="inlineStr"/>
       <c r="BN3" s="2" t="inlineStr"/>
       <c r="BO3" s="2" t="n">
@@ -1785,7 +1786,7 @@
       <c r="BK4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL4" s="2" t="inlineStr"/>
+      <c r="BL4" s="2" t="n"/>
       <c r="BM4" s="2" t="inlineStr"/>
       <c r="BN4" s="2" t="inlineStr"/>
       <c r="BO4" s="2" t="n">
@@ -2044,7 +2045,7 @@
       <c r="BK5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL5" s="2" t="inlineStr"/>
+      <c r="BL5" s="2" t="n"/>
       <c r="BM5" s="2" t="inlineStr"/>
       <c r="BN5" s="2" t="inlineStr"/>
       <c r="BO5" s="2" t="n">
@@ -2301,7 +2302,7 @@
       <c r="BK6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL6" s="2" t="inlineStr"/>
+      <c r="BL6" s="2" t="n"/>
       <c r="BM6" s="2" t="inlineStr"/>
       <c r="BN6" s="2" t="inlineStr"/>
       <c r="BO6" s="2" t="n">
@@ -2552,7 +2553,7 @@
       <c r="BK7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL7" s="2" t="inlineStr"/>
+      <c r="BL7" s="2" t="n"/>
       <c r="BM7" s="2" t="inlineStr"/>
       <c r="BN7" s="2" t="inlineStr"/>
       <c r="BO7" s="2" t="n">
@@ -2813,7 +2814,7 @@
       <c r="BK8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL8" s="2" t="inlineStr"/>
+      <c r="BL8" s="2" t="n"/>
       <c r="BM8" s="2" t="inlineStr"/>
       <c r="BN8" s="2" t="inlineStr"/>
       <c r="BO8" s="2" t="n">
@@ -3074,7 +3075,7 @@
       <c r="BK9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL9" s="2" t="inlineStr"/>
+      <c r="BL9" s="2" t="n"/>
       <c r="BM9" s="2" t="inlineStr"/>
       <c r="BN9" s="2" t="inlineStr"/>
       <c r="BO9" s="2" t="n">
@@ -3331,7 +3332,7 @@
       <c r="BK10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL10" s="2" t="inlineStr"/>
+      <c r="BL10" s="2" t="n"/>
       <c r="BM10" s="2" t="inlineStr"/>
       <c r="BN10" s="2" t="inlineStr"/>
       <c r="BO10" s="2" t="n">
@@ -3582,7 +3583,7 @@
           <t>4 OFICIO DE REG DE IMOVEIS</t>
         </is>
       </c>
-      <c r="BB11" s="4" t="n">
+      <c r="BB11" s="6" t="n">
         <v>38461</v>
       </c>
       <c r="BC11" s="2" t="inlineStr">
@@ -3607,7 +3608,7 @@
       <c r="BH11" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="BI11" s="4" t="n">
+      <c r="BI11" s="6" t="n">
         <v>35517</v>
       </c>
       <c r="BJ11" s="2" t="inlineStr">
@@ -3618,7 +3619,7 @@
       <c r="BK11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL11" s="2" t="inlineStr"/>
+      <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="inlineStr"/>
       <c r="BN11" s="2" t="inlineStr"/>
       <c r="BO11" s="2" t="n">
@@ -3807,7 +3808,7 @@
       <c r="BI12" s="2" t="inlineStr"/>
       <c r="BJ12" s="2" t="inlineStr"/>
       <c r="BK12" s="2" t="inlineStr"/>
-      <c r="BL12" s="2" t="inlineStr"/>
+      <c r="BL12" s="2" t="n"/>
       <c r="BM12" s="2" t="inlineStr"/>
       <c r="BN12" s="2" t="inlineStr"/>
       <c r="BO12" s="2" t="inlineStr"/>
@@ -4092,7 +4093,7 @@
           <t>5 OFICIO DE REG DE IMOVEIS</t>
         </is>
       </c>
-      <c r="BB13" s="4" t="n">
+      <c r="BB13" s="6" t="n">
         <v>36763</v>
       </c>
       <c r="BC13" s="2" t="inlineStr">
@@ -4117,7 +4118,7 @@
       <c r="BH13" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="BI13" s="4" t="n">
+      <c r="BI13" s="6" t="n">
         <v>43721.61274305556</v>
       </c>
       <c r="BJ13" s="2" t="inlineStr">
@@ -4128,9 +4129,9 @@
       <c r="BK13" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="BL13" s="2" t="inlineStr">
-        <is>
-          <t>7.02915572020807e+18; 7.08577362019807e+18; 7.32728092018807e+18; 20160111018656.0</t>
+      <c r="BL13" s="7" t="inlineStr">
+        <is>
+          <t>07029155720208070018; 07085773620198070018; 07327280920188070016; 20160111018656</t>
         </is>
       </c>
       <c r="BM13" s="2" t="inlineStr"/>
@@ -4141,7 +4142,7 @@
       <c r="BP13" s="2" t="n">
         <v>81785</v>
       </c>
-      <c r="BQ13" s="4" t="n">
+      <c r="BQ13" s="6" t="n">
         <v>36927</v>
       </c>
       <c r="BR13" s="2" t="inlineStr">
@@ -4363,7 +4364,7 @@
       <c r="BI14" s="2" t="inlineStr"/>
       <c r="BJ14" s="2" t="inlineStr"/>
       <c r="BK14" s="2" t="inlineStr"/>
-      <c r="BL14" s="2" t="inlineStr"/>
+      <c r="BL14" s="2" t="n"/>
       <c r="BM14" s="2" t="inlineStr"/>
       <c r="BN14" s="2" t="inlineStr"/>
       <c r="BO14" s="2" t="inlineStr"/>
@@ -4638,7 +4639,7 @@
           <t>6 OFICIO DE REG DE IMOVEIS</t>
         </is>
       </c>
-      <c r="BB15" s="4" t="n">
+      <c r="BB15" s="6" t="n">
         <v>41288</v>
       </c>
       <c r="BC15" s="2" t="inlineStr">
@@ -4666,7 +4667,7 @@
       <c r="BK15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL15" s="2" t="inlineStr"/>
+      <c r="BL15" s="2" t="n"/>
       <c r="BM15" s="2" t="inlineStr"/>
       <c r="BN15" s="2" t="inlineStr"/>
       <c r="BO15" s="2" t="n">
@@ -4943,7 +4944,7 @@
           <t>3 OFICIO DE REG DE IMOVEIS</t>
         </is>
       </c>
-      <c r="BB16" s="4" t="n">
+      <c r="BB16" s="6" t="n">
         <v>44557</v>
       </c>
       <c r="BC16" s="2" t="inlineStr">
@@ -4968,7 +4969,7 @@
       <c r="BH16" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="BI16" s="4" t="n">
+      <c r="BI16" s="6" t="n">
         <v>46174.39575231481</v>
       </c>
       <c r="BJ16" s="2" t="inlineStr">
@@ -4979,9 +4980,9 @@
       <c r="BK16" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="BL16" s="2" t="inlineStr">
-        <is>
-          <t>7.00710262018807e+18</t>
+      <c r="BL16" s="7" t="inlineStr">
+        <is>
+          <t>07007102620188070018</t>
         </is>
       </c>
       <c r="BM16" s="2" t="inlineStr"/>
@@ -4992,7 +4993,7 @@
       <c r="BP16" s="2" t="n">
         <v>95189</v>
       </c>
-      <c r="BQ16" s="4" t="n">
+      <c r="BQ16" s="6" t="n">
         <v>40526</v>
       </c>
       <c r="BR16" s="2" t="inlineStr">
@@ -5258,7 +5259,7 @@
           <t>2 OFICIO DE REG DE IMOVEIS</t>
         </is>
       </c>
-      <c r="BB17" s="4" t="n">
+      <c r="BB17" s="6" t="n">
         <v>37810</v>
       </c>
       <c r="BC17" s="2" t="inlineStr">
@@ -5283,7 +5284,7 @@
       <c r="BH17" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="BI17" s="4" t="n">
+      <c r="BI17" s="6" t="n">
         <v>45995.40071759259</v>
       </c>
       <c r="BJ17" s="2" t="inlineStr">
@@ -5294,7 +5295,7 @@
       <c r="BK17" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL17" s="2" t="inlineStr"/>
+      <c r="BL17" s="2" t="n"/>
       <c r="BM17" s="2" t="inlineStr"/>
       <c r="BN17" s="2" t="inlineStr"/>
       <c r="BO17" s="2" t="n">
@@ -5493,7 +5494,7 @@
       <c r="BI18" s="2" t="inlineStr"/>
       <c r="BJ18" s="2" t="inlineStr"/>
       <c r="BK18" s="2" t="inlineStr"/>
-      <c r="BL18" s="2" t="inlineStr"/>
+      <c r="BL18" s="2" t="n"/>
       <c r="BM18" s="2" t="inlineStr"/>
       <c r="BN18" s="2" t="inlineStr"/>
       <c r="BO18" s="2" t="inlineStr"/>
@@ -5752,7 +5753,7 @@
       <c r="BK19" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL19" s="2" t="inlineStr"/>
+      <c r="BL19" s="2" t="n"/>
       <c r="BM19" s="2" t="inlineStr"/>
       <c r="BN19" s="2" t="inlineStr"/>
       <c r="BO19" s="2" t="n">
@@ -6007,7 +6008,7 @@
       <c r="BK20" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL20" s="2" t="inlineStr"/>
+      <c r="BL20" s="2" t="n"/>
       <c r="BM20" s="2" t="inlineStr"/>
       <c r="BN20" s="2" t="inlineStr"/>
       <c r="BO20" s="2" t="n">
@@ -6268,7 +6269,7 @@
       <c r="BK21" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL21" s="2" t="inlineStr"/>
+      <c r="BL21" s="2" t="n"/>
       <c r="BM21" s="2" t="inlineStr"/>
       <c r="BN21" s="2" t="inlineStr"/>
       <c r="BO21" s="2" t="n">
@@ -6527,7 +6528,7 @@
       <c r="BK22" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL22" s="2" t="inlineStr"/>
+      <c r="BL22" s="2" t="n"/>
       <c r="BM22" s="2" t="inlineStr"/>
       <c r="BN22" s="2" t="inlineStr"/>
       <c r="BO22" s="2" t="n">
@@ -6786,7 +6787,7 @@
       <c r="BK23" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL23" s="2" t="inlineStr"/>
+      <c r="BL23" s="2" t="n"/>
       <c r="BM23" s="2" t="inlineStr"/>
       <c r="BN23" s="2" t="inlineStr"/>
       <c r="BO23" s="2" t="n">
@@ -7047,7 +7048,7 @@
       <c r="BK24" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL24" s="2" t="inlineStr"/>
+      <c r="BL24" s="2" t="n"/>
       <c r="BM24" s="2" t="inlineStr"/>
       <c r="BN24" s="2" t="inlineStr"/>
       <c r="BO24" s="2" t="n">
@@ -7308,7 +7309,7 @@
       <c r="BK25" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL25" s="2" t="inlineStr"/>
+      <c r="BL25" s="2" t="n"/>
       <c r="BM25" s="2" t="inlineStr"/>
       <c r="BN25" s="2" t="inlineStr"/>
       <c r="BO25" s="2" t="n">
@@ -7559,7 +7560,7 @@
       <c r="BK26" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL26" s="2" t="inlineStr"/>
+      <c r="BL26" s="2" t="n"/>
       <c r="BM26" s="2" t="inlineStr"/>
       <c r="BN26" s="2" t="inlineStr"/>
       <c r="BO26" s="2" t="n">
@@ -7820,7 +7821,7 @@
       <c r="BK27" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL27" s="2" t="inlineStr"/>
+      <c r="BL27" s="2" t="n"/>
       <c r="BM27" s="2" t="inlineStr"/>
       <c r="BN27" s="2" t="inlineStr"/>
       <c r="BO27" s="2" t="n">
@@ -8001,7 +8002,7 @@
       <c r="BI28" s="2" t="inlineStr"/>
       <c r="BJ28" s="2" t="inlineStr"/>
       <c r="BK28" s="2" t="inlineStr"/>
-      <c r="BL28" s="2" t="inlineStr"/>
+      <c r="BL28" s="2" t="n"/>
       <c r="BM28" s="2" t="inlineStr"/>
       <c r="BN28" s="2" t="inlineStr"/>
       <c r="BO28" s="2" t="inlineStr"/>
@@ -8214,7 +8215,7 @@
       <c r="BI29" s="2" t="inlineStr"/>
       <c r="BJ29" s="2" t="inlineStr"/>
       <c r="BK29" s="2" t="inlineStr"/>
-      <c r="BL29" s="2" t="inlineStr"/>
+      <c r="BL29" s="2" t="n"/>
       <c r="BM29" s="2" t="inlineStr"/>
       <c r="BN29" s="2" t="inlineStr"/>
       <c r="BO29" s="2" t="inlineStr"/>
@@ -8500,7 +8501,7 @@
       <c r="BH30" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="BI30" s="4" t="n">
+      <c r="BI30" s="6" t="n">
         <v>45653.57881944445</v>
       </c>
       <c r="BJ30" s="2" t="inlineStr">
@@ -8511,9 +8512,9 @@
       <c r="BK30" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="BL30" s="2" t="inlineStr">
-        <is>
-          <t>7.05104422019807e+18</t>
+      <c r="BL30" s="7" t="inlineStr">
+        <is>
+          <t>07051044220198070018</t>
         </is>
       </c>
       <c r="BM30" s="2" t="inlineStr"/>
@@ -8524,7 +8525,7 @@
       <c r="BP30" s="2" t="n">
         <v>94791</v>
       </c>
-      <c r="BQ30" s="4" t="n">
+      <c r="BQ30" s="6" t="n">
         <v>40542</v>
       </c>
       <c r="BR30" s="2" t="inlineStr">
@@ -8815,7 +8816,7 @@
       <c r="BH31" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="BI31" s="4" t="n">
+      <c r="BI31" s="6" t="n">
         <v>45007.386875</v>
       </c>
       <c r="BJ31" s="2" t="inlineStr">
@@ -8826,9 +8827,9 @@
       <c r="BK31" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="BL31" s="2" t="inlineStr">
-        <is>
-          <t>9853620125100000.0; 2.920037200351e+17; 20120110850350.0</t>
+      <c r="BL31" s="7" t="inlineStr">
+        <is>
+          <t>00009853620125100004; 00292003720035100004; 20120110850350</t>
         </is>
       </c>
       <c r="BM31" s="2" t="inlineStr"/>
@@ -9130,7 +9131,7 @@
       <c r="BH32" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="BI32" s="4" t="n">
+      <c r="BI32" s="6" t="n">
         <v>45007.386875</v>
       </c>
       <c r="BJ32" s="2" t="inlineStr">
@@ -9141,9 +9142,9 @@
       <c r="BK32" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="BL32" s="2" t="inlineStr">
-        <is>
-          <t>9853620125100000.0; 2.920037200351e+17; 20120110850350.0</t>
+      <c r="BL32" s="7" t="inlineStr">
+        <is>
+          <t>00009853620125100004; 00292003720035100004; 20120110850350</t>
         </is>
       </c>
       <c r="BM32" s="2" t="inlineStr"/>
@@ -9430,7 +9431,7 @@
           <t>6 OFICIO DE REG DE IMOVEIS</t>
         </is>
       </c>
-      <c r="BB33" s="4" t="n">
+      <c r="BB33" s="6" t="n">
         <v>41288</v>
       </c>
       <c r="BC33" s="2" t="inlineStr">
@@ -9458,7 +9459,7 @@
       <c r="BK33" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL33" s="2" t="inlineStr"/>
+      <c r="BL33" s="2" t="n"/>
       <c r="BM33" s="2" t="inlineStr"/>
       <c r="BN33" s="2" t="inlineStr"/>
       <c r="BO33" s="2" t="n">
@@ -9759,7 +9760,7 @@
       <c r="BK34" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL34" s="2" t="inlineStr"/>
+      <c r="BL34" s="2" t="n"/>
       <c r="BM34" s="2" t="inlineStr"/>
       <c r="BN34" s="2" t="inlineStr"/>
       <c r="BO34" s="2" t="n">
@@ -10042,7 +10043,7 @@
           <t>1 OFICIO DE REG DE IMOVEIS</t>
         </is>
       </c>
-      <c r="BB35" s="4" t="n">
+      <c r="BB35" s="6" t="n">
         <v>38236</v>
       </c>
       <c r="BC35" s="2" t="inlineStr">
@@ -10067,7 +10068,7 @@
       <c r="BH35" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="BI35" s="4" t="n">
+      <c r="BI35" s="6" t="n">
         <v>38244</v>
       </c>
       <c r="BJ35" s="2" t="inlineStr">
@@ -10078,9 +10079,9 @@
       <c r="BK35" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="BL35" s="2" t="inlineStr">
-        <is>
-          <t>7.05899772021807e+18; 7.09049282018807e+18; 7.33765172021807e+18; 19990110485822.0; 20020001481816.0; 20140020034910.0</t>
+      <c r="BL35" s="7" t="inlineStr">
+        <is>
+          <t>07058997720218070018; 07090492820188070000; 07337651720218070000; 19990110485822; 20020001481816; 20140020034910</t>
         </is>
       </c>
       <c r="BM35" s="2" t="inlineStr">
@@ -10358,7 +10359,7 @@
       <c r="BH36" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="BI36" s="4" t="n">
+      <c r="BI36" s="6" t="n">
         <v>46209.74333333333</v>
       </c>
       <c r="BJ36" s="2" t="inlineStr">
@@ -10370,7 +10371,7 @@
       <c r="BK36" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL36" s="2" t="inlineStr"/>
+      <c r="BL36" s="2" t="n"/>
       <c r="BM36" s="2" t="inlineStr"/>
       <c r="BN36" s="2" t="inlineStr"/>
       <c r="BO36" s="2" t="n">
@@ -10379,7 +10380,7 @@
       <c r="BP36" s="2" t="n">
         <v>27334</v>
       </c>
-      <c r="BQ36" s="4" t="n">
+      <c r="BQ36" s="6" t="n">
         <v>34043</v>
       </c>
       <c r="BR36" s="2" t="inlineStr">
@@ -10637,7 +10638,7 @@
       <c r="BK37" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL37" s="2" t="inlineStr"/>
+      <c r="BL37" s="2" t="n"/>
       <c r="BM37" s="2" t="inlineStr"/>
       <c r="BN37" s="2" t="inlineStr"/>
       <c r="BO37" s="2" t="n">
@@ -10892,7 +10893,7 @@
       <c r="BK38" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL38" s="2" t="inlineStr"/>
+      <c r="BL38" s="2" t="n"/>
       <c r="BM38" s="2" t="inlineStr"/>
       <c r="BN38" s="2" t="inlineStr"/>
       <c r="BO38" s="2" t="n">
@@ -11151,7 +11152,7 @@
       <c r="BK39" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL39" s="2" t="inlineStr"/>
+      <c r="BL39" s="2" t="n"/>
       <c r="BM39" s="2" t="inlineStr"/>
       <c r="BN39" s="2" t="inlineStr"/>
       <c r="BO39" s="2" t="n">
@@ -11412,7 +11413,7 @@
       <c r="BK40" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL40" s="2" t="inlineStr"/>
+      <c r="BL40" s="2" t="n"/>
       <c r="BM40" s="2" t="inlineStr"/>
       <c r="BN40" s="2" t="inlineStr"/>
       <c r="BO40" s="2" t="n">
@@ -11669,7 +11670,7 @@
       <c r="BK41" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL41" s="2" t="inlineStr"/>
+      <c r="BL41" s="2" t="n"/>
       <c r="BM41" s="2" t="inlineStr"/>
       <c r="BN41" s="2" t="inlineStr"/>
       <c r="BO41" s="2" t="n">
@@ -11930,7 +11931,7 @@
       <c r="BK42" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL42" s="2" t="inlineStr"/>
+      <c r="BL42" s="2" t="n"/>
       <c r="BM42" s="2" t="inlineStr"/>
       <c r="BN42" s="2" t="inlineStr"/>
       <c r="BO42" s="2" t="n">
@@ -12191,7 +12192,7 @@
       <c r="BK43" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL43" s="2" t="inlineStr"/>
+      <c r="BL43" s="2" t="n"/>
       <c r="BM43" s="2" t="inlineStr"/>
       <c r="BN43" s="2" t="inlineStr"/>
       <c r="BO43" s="2" t="n">
@@ -12452,7 +12453,7 @@
       <c r="BK44" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL44" s="2" t="inlineStr"/>
+      <c r="BL44" s="2" t="n"/>
       <c r="BM44" s="2" t="inlineStr"/>
       <c r="BN44" s="2" t="inlineStr"/>
       <c r="BO44" s="2" t="n">
@@ -12713,7 +12714,7 @@
       <c r="BK45" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL45" s="2" t="inlineStr"/>
+      <c r="BL45" s="2" t="n"/>
       <c r="BM45" s="2" t="inlineStr"/>
       <c r="BN45" s="2" t="inlineStr"/>
       <c r="BO45" s="2" t="n">
@@ -12982,7 +12983,7 @@
       <c r="BK46" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL46" s="2" t="inlineStr"/>
+      <c r="BL46" s="2" t="n"/>
       <c r="BM46" s="2" t="inlineStr"/>
       <c r="BN46" s="2" t="inlineStr"/>
       <c r="BO46" s="2" t="n">
@@ -13239,7 +13240,7 @@
       <c r="BK47" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL47" s="2" t="inlineStr"/>
+      <c r="BL47" s="2" t="n"/>
       <c r="BM47" s="2" t="inlineStr"/>
       <c r="BN47" s="2" t="inlineStr"/>
       <c r="BO47" s="2" t="n">
@@ -13490,7 +13491,7 @@
           <t>4 OFICIO DE REG DE IMOVEIS</t>
         </is>
       </c>
-      <c r="BB48" s="4" t="n">
+      <c r="BB48" s="6" t="n">
         <v>38461</v>
       </c>
       <c r="BC48" s="2" t="inlineStr">
@@ -13515,7 +13516,7 @@
       <c r="BH48" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="BI48" s="4" t="n">
+      <c r="BI48" s="6" t="n">
         <v>45544.44724537037</v>
       </c>
       <c r="BJ48" s="2" t="inlineStr">
@@ -13526,9 +13527,9 @@
       <c r="BK48" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="BL48" s="2" t="inlineStr">
-        <is>
-          <t>7.22833222021807e+18</t>
+      <c r="BL48" s="7" t="inlineStr">
+        <is>
+          <t>07228332220218070015</t>
         </is>
       </c>
       <c r="BM48" s="2" t="inlineStr"/>
@@ -13788,7 +13789,7 @@
       <c r="BH49" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="BI49" s="4" t="n">
+      <c r="BI49" s="6" t="n">
         <v>45315.50809027778</v>
       </c>
       <c r="BJ49" s="2" t="inlineStr">
@@ -13799,9 +13800,9 @@
       <c r="BK49" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="BL49" s="2" t="inlineStr">
-        <is>
-          <t>7.02224042024807e+18; 7.08525112017807e+18; 7.15870382024807e+18; 20160110396955.0</t>
+      <c r="BL49" s="7" t="inlineStr">
+        <is>
+          <t>07022240420248070018; 07085251120178070018; 07158703820248070000; 20160110396955</t>
         </is>
       </c>
       <c r="BM49" s="2" t="inlineStr"/>
@@ -13812,7 +13813,7 @@
       <c r="BP49" s="2" t="n">
         <v>94847</v>
       </c>
-      <c r="BQ49" s="4" t="n">
+      <c r="BQ49" s="6" t="n">
         <v>40556</v>
       </c>
       <c r="BR49" s="2" t="inlineStr">
@@ -14092,7 +14093,7 @@
           <t>6 OFICIO DE REG DE IMOVEIS</t>
         </is>
       </c>
-      <c r="BB50" s="4" t="n">
+      <c r="BB50" s="6" t="n">
         <v>41288</v>
       </c>
       <c r="BC50" s="2" t="inlineStr">
@@ -14120,7 +14121,7 @@
       <c r="BK50" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL50" s="2" t="inlineStr"/>
+      <c r="BL50" s="2" t="n"/>
       <c r="BM50" s="2" t="inlineStr"/>
       <c r="BN50" s="2" t="inlineStr"/>
       <c r="BO50" s="2" t="n">
@@ -14407,7 +14408,7 @@
           <t>2 OFICIO DE REG DE IMOVEIS</t>
         </is>
       </c>
-      <c r="BB51" s="4" t="n">
+      <c r="BB51" s="6" t="n">
         <v>37664</v>
       </c>
       <c r="BC51" s="2" t="inlineStr">
@@ -14432,7 +14433,7 @@
       <c r="BH51" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="BI51" s="4" t="n">
+      <c r="BI51" s="6" t="n">
         <v>42025.38631944444</v>
       </c>
       <c r="BJ51" s="2" t="inlineStr">
@@ -14443,7 +14444,7 @@
       <c r="BK51" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL51" s="2" t="inlineStr"/>
+      <c r="BL51" s="2" t="n"/>
       <c r="BM51" s="2" t="inlineStr"/>
       <c r="BN51" s="2" t="inlineStr"/>
       <c r="BO51" s="2" t="n">
@@ -14726,7 +14727,7 @@
           <t>2 OFICIO DE REG DE IMOVEIS</t>
         </is>
       </c>
-      <c r="BB52" s="4" t="n">
+      <c r="BB52" s="6" t="n">
         <v>37664</v>
       </c>
       <c r="BC52" s="2" t="inlineStr">
@@ -14751,7 +14752,7 @@
       <c r="BH52" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="BI52" s="4" t="n">
+      <c r="BI52" s="6" t="n">
         <v>45868.45605324074</v>
       </c>
       <c r="BJ52" s="2" t="inlineStr">
@@ -14762,9 +14763,9 @@
       <c r="BK52" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="BL52" s="2" t="inlineStr">
-        <is>
-          <t>7.38820722023807e+18</t>
+      <c r="BL52" s="7" t="inlineStr">
+        <is>
+          <t>07388207220238070001</t>
         </is>
       </c>
       <c r="BM52" s="2" t="inlineStr"/>
@@ -14775,7 +14776,7 @@
       <c r="BP52" s="2" t="n">
         <v>113551</v>
       </c>
-      <c r="BQ52" s="4" t="n">
+      <c r="BQ52" s="6" t="n">
         <v>44683</v>
       </c>
       <c r="BR52" s="2" t="inlineStr">
@@ -15066,7 +15067,7 @@
       <c r="BH53" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="BI53" s="4" t="n">
+      <c r="BI53" s="6" t="n">
         <v>45971.55646990741</v>
       </c>
       <c r="BJ53" s="2" t="inlineStr">
@@ -15077,9 +15078,9 @@
       <c r="BK53" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="BL53" s="2" t="inlineStr">
-        <is>
-          <t>7.05935222021807e+18; 20140110765974.0; 20170110329988.0</t>
+      <c r="BL53" s="7" t="inlineStr">
+        <is>
+          <t>07059352220218070018; 20140110765974; 20170110329988</t>
         </is>
       </c>
       <c r="BM53" s="2" t="inlineStr">
@@ -15358,7 +15359,7 @@
       <c r="BK54" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL54" s="2" t="inlineStr"/>
+      <c r="BL54" s="2" t="n"/>
       <c r="BM54" s="2" t="inlineStr"/>
       <c r="BN54" s="2" t="inlineStr"/>
       <c r="BO54" s="2" t="n">
@@ -15613,7 +15614,7 @@
       <c r="BK55" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL55" s="2" t="inlineStr"/>
+      <c r="BL55" s="2" t="n"/>
       <c r="BM55" s="2" t="inlineStr"/>
       <c r="BN55" s="2" t="inlineStr"/>
       <c r="BO55" s="2" t="n">
@@ -15868,7 +15869,7 @@
       <c r="BK56" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL56" s="2" t="inlineStr"/>
+      <c r="BL56" s="2" t="n"/>
       <c r="BM56" s="2" t="inlineStr"/>
       <c r="BN56" s="2" t="inlineStr"/>
       <c r="BO56" s="2" t="n">
@@ -16049,7 +16050,7 @@
       <c r="BI57" s="2" t="inlineStr"/>
       <c r="BJ57" s="2" t="inlineStr"/>
       <c r="BK57" s="2" t="inlineStr"/>
-      <c r="BL57" s="2" t="inlineStr"/>
+      <c r="BL57" s="2" t="n"/>
       <c r="BM57" s="2" t="inlineStr"/>
       <c r="BN57" s="2" t="inlineStr"/>
       <c r="BO57" s="2" t="inlineStr"/>
@@ -16310,7 +16311,7 @@
       <c r="BK58" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL58" s="2" t="inlineStr"/>
+      <c r="BL58" s="2" t="n"/>
       <c r="BM58" s="2" t="inlineStr"/>
       <c r="BN58" s="2" t="inlineStr"/>
       <c r="BO58" s="2" t="n">
@@ -16567,7 +16568,7 @@
       <c r="BK59" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL59" s="2" t="inlineStr"/>
+      <c r="BL59" s="2" t="n"/>
       <c r="BM59" s="2" t="inlineStr"/>
       <c r="BN59" s="2" t="inlineStr"/>
       <c r="BO59" s="2" t="n">
@@ -16818,7 +16819,7 @@
       <c r="BK60" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL60" s="2" t="inlineStr"/>
+      <c r="BL60" s="2" t="n"/>
       <c r="BM60" s="2" t="inlineStr"/>
       <c r="BN60" s="2" t="inlineStr"/>
       <c r="BO60" s="2" t="n">
@@ -17079,7 +17080,7 @@
       <c r="BK61" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL61" s="2" t="inlineStr"/>
+      <c r="BL61" s="2" t="n"/>
       <c r="BM61" s="2" t="inlineStr"/>
       <c r="BN61" s="2" t="inlineStr"/>
       <c r="BO61" s="2" t="n">
@@ -17345,7 +17346,7 @@
       <c r="BH62" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="BI62" s="4" t="n">
+      <c r="BI62" s="6" t="n">
         <v>43613.72193287037</v>
       </c>
       <c r="BJ62" s="2" t="inlineStr">
@@ -17356,9 +17357,9 @@
       <c r="BK62" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="BL62" s="2" t="inlineStr">
-        <is>
-          <t>7.00645602020807e+18; 20150111330483.0</t>
+      <c r="BL62" s="7" t="inlineStr">
+        <is>
+          <t>07006456020208070018; 20150111330483</t>
         </is>
       </c>
       <c r="BM62" s="2" t="inlineStr"/>
@@ -17369,7 +17370,7 @@
       <c r="BP62" s="2" t="n">
         <v>98554</v>
       </c>
-      <c r="BQ62" s="4" t="n">
+      <c r="BQ62" s="6" t="n">
         <v>42300</v>
       </c>
       <c r="BR62" s="2" t="inlineStr">
@@ -17591,7 +17592,7 @@
       <c r="BI63" s="2" t="inlineStr"/>
       <c r="BJ63" s="2" t="inlineStr"/>
       <c r="BK63" s="2" t="inlineStr"/>
-      <c r="BL63" s="2" t="inlineStr"/>
+      <c r="BL63" s="2" t="n"/>
       <c r="BM63" s="2" t="inlineStr"/>
       <c r="BN63" s="2" t="inlineStr"/>
       <c r="BO63" s="2" t="inlineStr"/>
@@ -17870,7 +17871,7 @@
           <t>2 OFICIO DE REG DE IMOVEIS</t>
         </is>
       </c>
-      <c r="BB64" s="4" t="n">
+      <c r="BB64" s="6" t="n">
         <v>37810</v>
       </c>
       <c r="BC64" s="2" t="inlineStr">
@@ -17895,7 +17896,7 @@
       <c r="BH64" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="BI64" s="4" t="n">
+      <c r="BI64" s="6" t="n">
         <v>42991.38122685185</v>
       </c>
       <c r="BJ64" s="2" t="inlineStr">
@@ -17906,7 +17907,7 @@
       <c r="BK64" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL64" s="2" t="inlineStr"/>
+      <c r="BL64" s="2" t="n"/>
       <c r="BM64" s="2" t="inlineStr"/>
       <c r="BN64" s="2" t="inlineStr"/>
       <c r="BO64" s="2" t="n">
@@ -18179,7 +18180,7 @@
           <t>2 OFICIO DE REG DE IMOVEIS</t>
         </is>
       </c>
-      <c r="BB65" s="4" t="n">
+      <c r="BB65" s="6" t="n">
         <v>37664</v>
       </c>
       <c r="BC65" s="2" t="inlineStr">
@@ -18204,7 +18205,7 @@
       <c r="BH65" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="BI65" s="4" t="n">
+      <c r="BI65" s="6" t="n">
         <v>42991.38122685185</v>
       </c>
       <c r="BJ65" s="2" t="inlineStr">
@@ -18215,7 +18216,7 @@
       <c r="BK65" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL65" s="2" t="inlineStr"/>
+      <c r="BL65" s="2" t="n"/>
       <c r="BM65" s="2" t="inlineStr"/>
       <c r="BN65" s="2" t="inlineStr"/>
       <c r="BO65" s="2" t="n">
@@ -18434,7 +18435,7 @@
       <c r="BI66" s="2" t="inlineStr"/>
       <c r="BJ66" s="2" t="inlineStr"/>
       <c r="BK66" s="2" t="inlineStr"/>
-      <c r="BL66" s="2" t="inlineStr"/>
+      <c r="BL66" s="2" t="n"/>
       <c r="BM66" s="2" t="inlineStr"/>
       <c r="BN66" s="2" t="inlineStr"/>
       <c r="BO66" s="2" t="inlineStr"/>
@@ -18714,7 +18715,7 @@
       <c r="BH67" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="BI67" s="4" t="n">
+      <c r="BI67" s="6" t="n">
         <v>44845.75594907408</v>
       </c>
       <c r="BJ67" s="2" t="inlineStr">
@@ -18725,9 +18726,9 @@
       <c r="BK67" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="BL67" s="2" t="inlineStr">
-        <is>
-          <t>1.095402020251e+18; 7.00636982020807e+18; 7.03334772020807e+18; 7.18170162024807e+18; 7.22464972026807e+18; 7.23984052020807e+18; 7.50500232024807e+18; 19980110018745.0; 20130110296220.0; 20130110603603.0; 20140111970194.0</t>
+      <c r="BL67" s="7" t="inlineStr">
+        <is>
+          <t>01095402020251000000; 07006369820208070018; 07033347720208070018; 07181701620248070018; 07224649720268070000; 07239840520208070000; 07505002320248070000; 19980110018745; 20130110296220; 20130110603603; 20140111970194</t>
         </is>
       </c>
       <c r="BM67" s="2" t="inlineStr">
@@ -18742,7 +18743,7 @@
       <c r="BP67" s="2" t="n">
         <v>65564</v>
       </c>
-      <c r="BQ67" s="4" t="n">
+      <c r="BQ67" s="6" t="n">
         <v>34711</v>
       </c>
       <c r="BR67" s="2" t="inlineStr">
@@ -19024,7 +19025,7 @@
           <t>2 OFICIO DE REG DE IMOVEIS</t>
         </is>
       </c>
-      <c r="BB68" s="4" t="n">
+      <c r="BB68" s="6" t="n">
         <v>44188</v>
       </c>
       <c r="BC68" s="2" t="inlineStr">
@@ -19051,7 +19052,7 @@
       <c r="BH68" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="BI68" s="4" t="n">
+      <c r="BI68" s="6" t="n">
         <v>46083.42450231482</v>
       </c>
       <c r="BJ68" s="2" t="inlineStr">
@@ -19062,7 +19063,7 @@
       <c r="BK68" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL68" s="2" t="inlineStr"/>
+      <c r="BL68" s="2" t="n"/>
       <c r="BM68" s="2" t="inlineStr"/>
       <c r="BN68" s="2" t="inlineStr"/>
       <c r="BO68" s="2" t="n">
@@ -19071,7 +19072,7 @@
       <c r="BP68" s="2" t="n">
         <v>5389</v>
       </c>
-      <c r="BQ68" s="4" t="n">
+      <c r="BQ68" s="6" t="n">
         <v>29478</v>
       </c>
       <c r="BR68" s="2" t="inlineStr">
@@ -19321,7 +19322,7 @@
       <c r="BK69" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL69" s="2" t="inlineStr"/>
+      <c r="BL69" s="2" t="n"/>
       <c r="BM69" s="2" t="inlineStr"/>
       <c r="BN69" s="2" t="inlineStr"/>
       <c r="BO69" s="2" t="n">
@@ -19576,7 +19577,7 @@
       <c r="BK70" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL70" s="2" t="inlineStr"/>
+      <c r="BL70" s="2" t="n"/>
       <c r="BM70" s="2" t="inlineStr"/>
       <c r="BN70" s="2" t="inlineStr"/>
       <c r="BO70" s="2" t="n">
@@ -19831,7 +19832,7 @@
       <c r="BK71" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL71" s="2" t="inlineStr"/>
+      <c r="BL71" s="2" t="n"/>
       <c r="BM71" s="2" t="inlineStr"/>
       <c r="BN71" s="2" t="inlineStr"/>
       <c r="BO71" s="2" t="n">
@@ -20024,7 +20025,7 @@
       <c r="BI72" s="2" t="inlineStr"/>
       <c r="BJ72" s="2" t="inlineStr"/>
       <c r="BK72" s="2" t="inlineStr"/>
-      <c r="BL72" s="2" t="inlineStr"/>
+      <c r="BL72" s="2" t="n"/>
       <c r="BM72" s="2" t="inlineStr"/>
       <c r="BN72" s="2" t="inlineStr"/>
       <c r="BO72" s="2" t="inlineStr"/>
@@ -20285,7 +20286,7 @@
       <c r="BK73" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL73" s="2" t="inlineStr"/>
+      <c r="BL73" s="2" t="n"/>
       <c r="BM73" s="2" t="inlineStr"/>
       <c r="BN73" s="2" t="inlineStr"/>
       <c r="BO73" s="2" t="n">
@@ -20536,7 +20537,7 @@
       <c r="BK74" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL74" s="2" t="inlineStr"/>
+      <c r="BL74" s="2" t="n"/>
       <c r="BM74" s="2" t="inlineStr"/>
       <c r="BN74" s="2" t="inlineStr"/>
       <c r="BO74" s="2" t="n">
@@ -20795,7 +20796,7 @@
       <c r="BK75" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL75" s="2" t="inlineStr"/>
+      <c r="BL75" s="2" t="n"/>
       <c r="BM75" s="2" t="inlineStr"/>
       <c r="BN75" s="2" t="inlineStr"/>
       <c r="BO75" s="2" t="n">
@@ -21060,7 +21061,7 @@
       <c r="BK76" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL76" s="2" t="inlineStr"/>
+      <c r="BL76" s="2" t="n"/>
       <c r="BM76" s="2" t="inlineStr"/>
       <c r="BN76" s="2" t="inlineStr"/>
       <c r="BO76" s="2" t="n">
@@ -21307,7 +21308,7 @@
           <t>4 OFICIO DE REG DE IMOVEIS</t>
         </is>
       </c>
-      <c r="BB77" s="4" t="n">
+      <c r="BB77" s="6" t="n">
         <v>38461</v>
       </c>
       <c r="BC77" s="2" t="inlineStr">
@@ -21332,7 +21333,7 @@
       <c r="BH77" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="BI77" s="4" t="n">
+      <c r="BI77" s="6" t="n">
         <v>35517</v>
       </c>
       <c r="BJ77" s="2" t="inlineStr">
@@ -21343,7 +21344,7 @@
       <c r="BK77" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL77" s="2" t="inlineStr"/>
+      <c r="BL77" s="2" t="n"/>
       <c r="BM77" s="2" t="inlineStr"/>
       <c r="BN77" s="2" t="inlineStr"/>
       <c r="BO77" s="2" t="n">
@@ -21532,7 +21533,7 @@
       <c r="BI78" s="2" t="inlineStr"/>
       <c r="BJ78" s="2" t="inlineStr"/>
       <c r="BK78" s="2" t="inlineStr"/>
-      <c r="BL78" s="2" t="inlineStr"/>
+      <c r="BL78" s="2" t="n"/>
       <c r="BM78" s="2" t="inlineStr"/>
       <c r="BN78" s="2" t="inlineStr"/>
       <c r="BO78" s="2" t="inlineStr"/>
@@ -21707,7 +21708,7 @@
       <c r="BI79" s="2" t="inlineStr"/>
       <c r="BJ79" s="2" t="inlineStr"/>
       <c r="BK79" s="2" t="inlineStr"/>
-      <c r="BL79" s="2" t="inlineStr"/>
+      <c r="BL79" s="2" t="n"/>
       <c r="BM79" s="2" t="inlineStr"/>
       <c r="BN79" s="2" t="inlineStr"/>
       <c r="BO79" s="2" t="inlineStr"/>
@@ -21963,7 +21964,7 @@
       <c r="BH80" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="BI80" s="4" t="n">
+      <c r="BI80" s="6" t="n">
         <v>43962.41179398148</v>
       </c>
       <c r="BJ80" s="2" t="inlineStr">
@@ -21975,7 +21976,7 @@
       <c r="BK80" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL80" s="2" t="inlineStr"/>
+      <c r="BL80" s="2" t="n"/>
       <c r="BM80" s="2" t="inlineStr"/>
       <c r="BN80" s="2" t="inlineStr"/>
       <c r="BO80" s="2" t="n">
@@ -21984,7 +21985,7 @@
       <c r="BP80" s="2" t="n">
         <v>94785</v>
       </c>
-      <c r="BQ80" s="4" t="n">
+      <c r="BQ80" s="6" t="n">
         <v>40528</v>
       </c>
       <c r="BR80" s="2" t="inlineStr">
@@ -22206,7 +22207,7 @@
       <c r="BI81" s="2" t="inlineStr"/>
       <c r="BJ81" s="2" t="inlineStr"/>
       <c r="BK81" s="2" t="inlineStr"/>
-      <c r="BL81" s="2" t="inlineStr"/>
+      <c r="BL81" s="2" t="n"/>
       <c r="BM81" s="2" t="inlineStr"/>
       <c r="BN81" s="2" t="inlineStr"/>
       <c r="BO81" s="2" t="inlineStr"/>
@@ -22461,7 +22462,7 @@
           <t>6 OFICIO DE REG DE IMOVEIS</t>
         </is>
       </c>
-      <c r="BB82" s="4" t="n">
+      <c r="BB82" s="6" t="n">
         <v>41288</v>
       </c>
       <c r="BC82" s="2" t="inlineStr">
@@ -22489,7 +22490,7 @@
       <c r="BK82" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL82" s="2" t="inlineStr"/>
+      <c r="BL82" s="2" t="n"/>
       <c r="BM82" s="2" t="inlineStr"/>
       <c r="BN82" s="2" t="inlineStr"/>
       <c r="BO82" s="2" t="n">
@@ -22769,7 +22770,7 @@
       <c r="BH83" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="BI83" s="4" t="n">
+      <c r="BI83" s="6" t="n">
         <v>46161.61016203704</v>
       </c>
       <c r="BJ83" s="2" t="inlineStr">
@@ -22780,7 +22781,7 @@
       <c r="BK83" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL83" s="2" t="inlineStr"/>
+      <c r="BL83" s="2" t="n"/>
       <c r="BM83" s="2" t="inlineStr"/>
       <c r="BN83" s="2" t="inlineStr"/>
       <c r="BO83" s="2" t="n">
@@ -22789,7 +22790,7 @@
       <c r="BP83" s="2" t="n">
         <v>112959</v>
       </c>
-      <c r="BQ83" s="4" t="n">
+      <c r="BQ83" s="6" t="n">
         <v>45202</v>
       </c>
       <c r="BR83" s="2" t="inlineStr">
@@ -23045,7 +23046,7 @@
           <t>1 OFICIO DE REG DE IMOVEIS</t>
         </is>
       </c>
-      <c r="BB84" s="4" t="n">
+      <c r="BB84" s="6" t="n">
         <v>35102</v>
       </c>
       <c r="BC84" s="2" t="inlineStr">
@@ -23070,7 +23071,7 @@
       <c r="BH84" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="BI84" s="4" t="n">
+      <c r="BI84" s="6" t="n">
         <v>45860.38936342593</v>
       </c>
       <c r="BJ84" s="2" t="inlineStr">
@@ -23081,7 +23082,7 @@
       <c r="BK84" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL84" s="2" t="inlineStr"/>
+      <c r="BL84" s="2" t="n"/>
       <c r="BM84" s="2" t="inlineStr"/>
       <c r="BN84" s="2" t="inlineStr"/>
       <c r="BO84" s="2" t="n">
@@ -23330,7 +23331,7 @@
           <t>3 OFICIO DE REG DE IMOVEIS</t>
         </is>
       </c>
-      <c r="BB85" s="4" t="n">
+      <c r="BB85" s="6" t="n">
         <v>27004</v>
       </c>
       <c r="BC85" s="2" t="inlineStr"/>
@@ -23353,7 +23354,7 @@
       <c r="BH85" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="BI85" s="4" t="n">
+      <c r="BI85" s="6" t="n">
         <v>44433.45929398148</v>
       </c>
       <c r="BJ85" s="2" t="inlineStr">
@@ -23364,9 +23365,9 @@
       <c r="BK85" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="BL85" s="2" t="inlineStr">
-        <is>
-          <t>20130110928657.0</t>
+      <c r="BL85" s="7" t="inlineStr">
+        <is>
+          <t>20130110928657</t>
         </is>
       </c>
       <c r="BM85" s="2" t="inlineStr"/>
@@ -23377,7 +23378,7 @@
       <c r="BP85" s="2" t="n">
         <v>33723</v>
       </c>
-      <c r="BQ85" s="4" t="n">
+      <c r="BQ85" s="6" t="n">
         <v>33368</v>
       </c>
       <c r="BR85" s="2" t="inlineStr">
@@ -23671,7 +23672,7 @@
       <c r="BK86" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL86" s="2" t="inlineStr"/>
+      <c r="BL86" s="2" t="n"/>
       <c r="BM86" s="2" t="inlineStr"/>
       <c r="BN86" s="2" t="inlineStr"/>
       <c r="BO86" s="2" t="n">
@@ -23936,7 +23937,7 @@
       <c r="BK87" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL87" s="2" t="inlineStr"/>
+      <c r="BL87" s="2" t="n"/>
       <c r="BM87" s="2" t="inlineStr"/>
       <c r="BN87" s="2" t="inlineStr"/>
       <c r="BO87" s="2" t="n">
@@ -24195,7 +24196,7 @@
       <c r="BK88" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL88" s="2" t="inlineStr"/>
+      <c r="BL88" s="2" t="n"/>
       <c r="BM88" s="2" t="inlineStr"/>
       <c r="BN88" s="2" t="inlineStr"/>
       <c r="BO88" s="2" t="n">
@@ -24454,7 +24455,7 @@
       <c r="BK89" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL89" s="2" t="inlineStr"/>
+      <c r="BL89" s="2" t="n"/>
       <c r="BM89" s="2" t="inlineStr"/>
       <c r="BN89" s="2" t="inlineStr"/>
       <c r="BO89" s="2" t="n">
@@ -24715,7 +24716,7 @@
       <c r="BK90" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL90" s="2" t="inlineStr"/>
+      <c r="BL90" s="2" t="n"/>
       <c r="BM90" s="2" t="inlineStr"/>
       <c r="BN90" s="2" t="inlineStr"/>
       <c r="BO90" s="2" t="n">
@@ -24966,7 +24967,7 @@
       <c r="BK91" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL91" s="2" t="inlineStr"/>
+      <c r="BL91" s="2" t="n"/>
       <c r="BM91" s="2" t="inlineStr"/>
       <c r="BN91" s="2" t="inlineStr"/>
       <c r="BO91" s="2" t="n">
@@ -25231,7 +25232,7 @@
       <c r="BK92" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL92" s="2" t="inlineStr"/>
+      <c r="BL92" s="2" t="n"/>
       <c r="BM92" s="2" t="inlineStr"/>
       <c r="BN92" s="2" t="inlineStr"/>
       <c r="BO92" s="2" t="n">
@@ -25489,7 +25490,7 @@
       <c r="BH93" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="BI93" s="4" t="n">
+      <c r="BI93" s="6" t="n">
         <v>45007.386875</v>
       </c>
       <c r="BJ93" s="2" t="inlineStr">
@@ -25500,9 +25501,9 @@
       <c r="BK93" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="BL93" s="2" t="inlineStr">
-        <is>
-          <t>9853620125100000.0; 2.920037200351e+17; 20120110850350.0</t>
+      <c r="BL93" s="7" t="inlineStr">
+        <is>
+          <t>00009853620125100004; 00292003720035100004; 20120110850350</t>
         </is>
       </c>
       <c r="BM93" s="2" t="inlineStr"/>
@@ -25789,7 +25790,7 @@
           <t>6 OFICIO DE REG DE IMOVEIS</t>
         </is>
       </c>
-      <c r="BB94" s="4" t="n">
+      <c r="BB94" s="6" t="n">
         <v>41288</v>
       </c>
       <c r="BC94" s="2" t="inlineStr">
@@ -25817,7 +25818,7 @@
       <c r="BK94" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL94" s="2" t="inlineStr"/>
+      <c r="BL94" s="2" t="n"/>
       <c r="BM94" s="2" t="inlineStr"/>
       <c r="BN94" s="2" t="inlineStr"/>
       <c r="BO94" s="2" t="n">
@@ -26096,7 +26097,7 @@
           <t>6 OFICIO DE REG DE IMOVEIS</t>
         </is>
       </c>
-      <c r="BB95" s="4" t="n">
+      <c r="BB95" s="6" t="n">
         <v>41288</v>
       </c>
       <c r="BC95" s="2" t="inlineStr">
@@ -26124,7 +26125,7 @@
       <c r="BK95" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL95" s="2" t="inlineStr"/>
+      <c r="BL95" s="2" t="n"/>
       <c r="BM95" s="2" t="inlineStr"/>
       <c r="BN95" s="2" t="inlineStr"/>
       <c r="BO95" s="2" t="n">
@@ -26403,7 +26404,7 @@
           <t>6 OFICIO DE REG DE IMOVEIS</t>
         </is>
       </c>
-      <c r="BB96" s="4" t="n">
+      <c r="BB96" s="6" t="n">
         <v>41288</v>
       </c>
       <c r="BC96" s="2" t="inlineStr">
@@ -26431,7 +26432,7 @@
       <c r="BK96" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL96" s="2" t="inlineStr"/>
+      <c r="BL96" s="2" t="n"/>
       <c r="BM96" s="2" t="inlineStr"/>
       <c r="BN96" s="2" t="inlineStr"/>
       <c r="BO96" s="2" t="n">
@@ -26714,7 +26715,7 @@
           <t>6 OFICIO DE REG DE IMOVEIS</t>
         </is>
       </c>
-      <c r="BB97" s="4" t="n">
+      <c r="BB97" s="6" t="n">
         <v>41288</v>
       </c>
       <c r="BC97" s="2" t="inlineStr">
@@ -26742,7 +26743,7 @@
       <c r="BK97" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL97" s="2" t="inlineStr"/>
+      <c r="BL97" s="2" t="n"/>
       <c r="BM97" s="2" t="inlineStr"/>
       <c r="BN97" s="2" t="inlineStr"/>
       <c r="BO97" s="2" t="n">
@@ -27028,7 +27029,7 @@
       <c r="BH98" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="BI98" s="4" t="n">
+      <c r="BI98" s="6" t="n">
         <v>44109.39166666667</v>
       </c>
       <c r="BJ98" s="2" t="inlineStr">
@@ -27039,7 +27040,7 @@
       <c r="BK98" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL98" s="2" t="inlineStr"/>
+      <c r="BL98" s="2" t="n"/>
       <c r="BM98" s="2" t="inlineStr"/>
       <c r="BN98" s="2" t="inlineStr"/>
       <c r="BO98" s="2" t="n">
@@ -27246,7 +27247,7 @@
       <c r="BI99" s="2" t="inlineStr"/>
       <c r="BJ99" s="2" t="inlineStr"/>
       <c r="BK99" s="2" t="inlineStr"/>
-      <c r="BL99" s="2" t="inlineStr"/>
+      <c r="BL99" s="2" t="n"/>
       <c r="BM99" s="2" t="inlineStr"/>
       <c r="BN99" s="2" t="inlineStr"/>
       <c r="BO99" s="2" t="inlineStr"/>
@@ -27506,7 +27507,7 @@
       <c r="BH100" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="BI100" s="4" t="n">
+      <c r="BI100" s="6" t="n">
         <v>46206.56833333334</v>
       </c>
       <c r="BJ100" s="2" t="inlineStr">
@@ -27517,9 +27518,9 @@
       <c r="BK100" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="BL100" s="2" t="inlineStr">
-        <is>
-          <t>7.44062982022807e+18; 7.50611612021807e+18</t>
+      <c r="BL100" s="7" t="inlineStr">
+        <is>
+          <t>07440629820228070016; 07506116120218070016</t>
         </is>
       </c>
       <c r="BM100" s="2" t="inlineStr"/>
@@ -27810,7 +27811,7 @@
           <t>6 OFICIO DE REG DE IMOVEIS</t>
         </is>
       </c>
-      <c r="BB101" s="4" t="n">
+      <c r="BB101" s="6" t="n">
         <v>37662</v>
       </c>
       <c r="BC101" s="2" t="inlineStr">
@@ -27838,7 +27839,7 @@
       <c r="BK101" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL101" s="2" t="inlineStr"/>
+      <c r="BL101" s="2" t="n"/>
       <c r="BM101" s="2" t="inlineStr"/>
       <c r="BN101" s="2" t="inlineStr"/>
       <c r="BO101" s="2" t="n">
@@ -28099,7 +28100,7 @@
       <c r="BK102" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL102" s="2" t="inlineStr"/>
+      <c r="BL102" s="2" t="n"/>
       <c r="BM102" s="2" t="inlineStr"/>
       <c r="BN102" s="2" t="inlineStr"/>
       <c r="BO102" s="2" t="n">
@@ -28359,7 +28360,7 @@
       <c r="BK103" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL103" s="2" t="inlineStr"/>
+      <c r="BL103" s="2" t="n"/>
       <c r="BM103" s="2" t="inlineStr"/>
       <c r="BN103" s="2" t="inlineStr"/>
       <c r="BO103" s="2" t="n">
@@ -28618,7 +28619,7 @@
       <c r="BK104" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL104" s="2" t="inlineStr"/>
+      <c r="BL104" s="2" t="n"/>
       <c r="BM104" s="2" t="inlineStr"/>
       <c r="BN104" s="2" t="inlineStr"/>
       <c r="BO104" s="2" t="n">
@@ -28873,7 +28874,7 @@
       <c r="BK105" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL105" s="2" t="inlineStr"/>
+      <c r="BL105" s="2" t="n"/>
       <c r="BM105" s="2" t="inlineStr"/>
       <c r="BN105" s="2" t="inlineStr"/>
       <c r="BO105" s="2" t="n">
@@ -29106,7 +29107,7 @@
           <t>3 OFICIO DE REG DE IMOVEIS</t>
         </is>
       </c>
-      <c r="BB106" s="4" t="n">
+      <c r="BB106" s="6" t="n">
         <v>28906</v>
       </c>
       <c r="BC106" s="2" t="inlineStr">
@@ -29131,7 +29132,7 @@
       <c r="BH106" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="BI106" s="4" t="n">
+      <c r="BI106" s="6" t="n">
         <v>42991.38122685185</v>
       </c>
       <c r="BJ106" s="2" t="inlineStr">
@@ -29142,7 +29143,7 @@
       <c r="BK106" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL106" s="2" t="inlineStr"/>
+      <c r="BL106" s="2" t="n"/>
       <c r="BM106" s="2" t="inlineStr"/>
       <c r="BN106" s="2" t="inlineStr"/>
       <c r="BO106" s="2" t="n">
@@ -29389,7 +29390,7 @@
           <t>4 OFICIO DE REG DE IMOVEIS</t>
         </is>
       </c>
-      <c r="BB107" s="4" t="n">
+      <c r="BB107" s="6" t="n">
         <v>38461</v>
       </c>
       <c r="BC107" s="2" t="inlineStr">
@@ -29414,7 +29415,7 @@
       <c r="BH107" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="BI107" s="4" t="n">
+      <c r="BI107" s="6" t="n">
         <v>35517</v>
       </c>
       <c r="BJ107" s="2" t="inlineStr">
@@ -29425,7 +29426,7 @@
       <c r="BK107" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL107" s="2" t="inlineStr"/>
+      <c r="BL107" s="2" t="n"/>
       <c r="BM107" s="2" t="inlineStr"/>
       <c r="BN107" s="2" t="inlineStr"/>
       <c r="BO107" s="2" t="n">
@@ -29683,7 +29684,7 @@
       <c r="BH108" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="BI108" s="4" t="n">
+      <c r="BI108" s="6" t="n">
         <v>42991.38122685185</v>
       </c>
       <c r="BJ108" s="2" t="inlineStr">
@@ -29694,7 +29695,7 @@
       <c r="BK108" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL108" s="2" t="inlineStr"/>
+      <c r="BL108" s="2" t="n"/>
       <c r="BM108" s="2" t="inlineStr"/>
       <c r="BN108" s="2" t="inlineStr"/>
       <c r="BO108" s="2" t="n">
@@ -29965,7 +29966,7 @@
           <t>3 OFICIO DE REG DE IMOVEIS</t>
         </is>
       </c>
-      <c r="BB109" s="4" t="n">
+      <c r="BB109" s="6" t="n">
         <v>35103</v>
       </c>
       <c r="BC109" s="2" t="inlineStr">
@@ -29990,7 +29991,7 @@
       <c r="BH109" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="BI109" s="4" t="n">
+      <c r="BI109" s="6" t="n">
         <v>43518.71640046296</v>
       </c>
       <c r="BJ109" s="2" t="inlineStr">
@@ -30001,9 +30002,9 @@
       <c r="BK109" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="BL109" s="2" t="inlineStr">
-        <is>
-          <t>7.10340432017807e+18; 7.50612462021807e+18; 20100110093278.0</t>
+      <c r="BL109" s="7" t="inlineStr">
+        <is>
+          <t>07103404320178070018; 07506124620218070016; 20100110093278</t>
         </is>
       </c>
       <c r="BM109" s="2" t="inlineStr"/>
@@ -30290,7 +30291,7 @@
           <t>2 OFICIO DE REG DE IMOVEIS</t>
         </is>
       </c>
-      <c r="BB110" s="4" t="n">
+      <c r="BB110" s="6" t="n">
         <v>37664</v>
       </c>
       <c r="BC110" s="2" t="inlineStr">
@@ -30315,7 +30316,7 @@
       <c r="BH110" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="BI110" s="4" t="n">
+      <c r="BI110" s="6" t="n">
         <v>43038.71349537037</v>
       </c>
       <c r="BJ110" s="2" t="inlineStr">
@@ -30326,7 +30327,7 @@
       <c r="BK110" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL110" s="2" t="inlineStr"/>
+      <c r="BL110" s="2" t="n"/>
       <c r="BM110" s="2" t="inlineStr"/>
       <c r="BN110" s="2" t="inlineStr"/>
       <c r="BO110" s="2" t="n">
@@ -30545,7 +30546,7 @@
       <c r="BI111" s="2" t="inlineStr"/>
       <c r="BJ111" s="2" t="inlineStr"/>
       <c r="BK111" s="2" t="inlineStr"/>
-      <c r="BL111" s="2" t="inlineStr"/>
+      <c r="BL111" s="2" t="n"/>
       <c r="BM111" s="2" t="inlineStr"/>
       <c r="BN111" s="2" t="inlineStr"/>
       <c r="BO111" s="2" t="inlineStr"/>
@@ -30794,7 +30795,7 @@
           <t>2 OFICIO DE REG DE IMOVEIS</t>
         </is>
       </c>
-      <c r="BB112" s="4" t="n">
+      <c r="BB112" s="6" t="n">
         <v>37664</v>
       </c>
       <c r="BC112" s="2" t="inlineStr">
@@ -30819,7 +30820,7 @@
       <c r="BH112" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="BI112" s="4" t="n">
+      <c r="BI112" s="6" t="n">
         <v>45868.46821759259</v>
       </c>
       <c r="BJ112" s="2" t="inlineStr">
@@ -30830,9 +30831,9 @@
       <c r="BK112" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="BL112" s="2" t="inlineStr">
-        <is>
-          <t>7.38820722023807e+18</t>
+      <c r="BL112" s="7" t="inlineStr">
+        <is>
+          <t>07388207220238070001</t>
         </is>
       </c>
       <c r="BM112" s="2" t="inlineStr"/>
@@ -30843,7 +30844,7 @@
       <c r="BP112" s="2" t="n">
         <v>113550</v>
       </c>
-      <c r="BQ112" s="4" t="n">
+      <c r="BQ112" s="6" t="n">
         <v>44683</v>
       </c>
       <c r="BR112" s="2" t="inlineStr">
@@ -31117,7 +31118,7 @@
           <t>2 OFICIO DE REG DE IMOVEIS</t>
         </is>
       </c>
-      <c r="BB113" s="4" t="n">
+      <c r="BB113" s="6" t="n">
         <v>37664</v>
       </c>
       <c r="BC113" s="2" t="inlineStr">
@@ -31142,7 +31143,7 @@
       <c r="BH113" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="BI113" s="4" t="n">
+      <c r="BI113" s="6" t="n">
         <v>45868.46273148148</v>
       </c>
       <c r="BJ113" s="2" t="inlineStr">
@@ -31153,9 +31154,9 @@
       <c r="BK113" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="BL113" s="2" t="inlineStr">
-        <is>
-          <t>7.38820722023807e+18</t>
+      <c r="BL113" s="7" t="inlineStr">
+        <is>
+          <t>07388207220238070001</t>
         </is>
       </c>
       <c r="BM113" s="2" t="inlineStr"/>
@@ -31166,7 +31167,7 @@
       <c r="BP113" s="2" t="n">
         <v>113549</v>
       </c>
-      <c r="BQ113" s="4" t="n">
+      <c r="BQ113" s="6" t="n">
         <v>44683</v>
       </c>
       <c r="BR113" s="2" t="inlineStr">
@@ -31451,7 +31452,7 @@
       <c r="BH114" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="BI114" s="4" t="n">
+      <c r="BI114" s="6" t="n">
         <v>42991.38122685185</v>
       </c>
       <c r="BJ114" s="2" t="inlineStr">
@@ -31462,7 +31463,7 @@
       <c r="BK114" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL114" s="2" t="inlineStr"/>
+      <c r="BL114" s="2" t="n"/>
       <c r="BM114" s="2" t="inlineStr"/>
       <c r="BN114" s="2" t="inlineStr"/>
       <c r="BO114" s="2" t="n">
@@ -31711,7 +31712,7 @@
       <c r="BK115" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL115" s="2" t="inlineStr"/>
+      <c r="BL115" s="2" t="n"/>
       <c r="BM115" s="2" t="inlineStr"/>
       <c r="BN115" s="2" t="inlineStr"/>
       <c r="BO115" s="2" t="n">
@@ -31966,7 +31967,7 @@
       <c r="BK116" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL116" s="2" t="inlineStr"/>
+      <c r="BL116" s="2" t="n"/>
       <c r="BM116" s="2" t="inlineStr"/>
       <c r="BN116" s="2" t="inlineStr"/>
       <c r="BO116" s="2" t="n">
@@ -32147,7 +32148,7 @@
       <c r="BI117" s="2" t="inlineStr"/>
       <c r="BJ117" s="2" t="inlineStr"/>
       <c r="BK117" s="2" t="inlineStr"/>
-      <c r="BL117" s="2" t="inlineStr"/>
+      <c r="BL117" s="2" t="n"/>
       <c r="BM117" s="2" t="inlineStr"/>
       <c r="BN117" s="2" t="inlineStr"/>
       <c r="BO117" s="2" t="inlineStr"/>
@@ -32416,7 +32417,7 @@
       <c r="BK118" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL118" s="2" t="inlineStr"/>
+      <c r="BL118" s="2" t="n"/>
       <c r="BM118" s="2" t="inlineStr"/>
       <c r="BN118" s="2" t="inlineStr"/>
       <c r="BO118" s="2" t="n">
@@ -32681,7 +32682,7 @@
       <c r="BK119" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL119" s="2" t="inlineStr"/>
+      <c r="BL119" s="2" t="n"/>
       <c r="BM119" s="2" t="inlineStr"/>
       <c r="BN119" s="2" t="inlineStr"/>
       <c r="BO119" s="2" t="n">
@@ -32932,7 +32933,7 @@
           <t>4 OFICIO DE REG DE IMOVEIS</t>
         </is>
       </c>
-      <c r="BB120" s="4" t="n">
+      <c r="BB120" s="6" t="n">
         <v>38461</v>
       </c>
       <c r="BC120" s="2" t="inlineStr">
@@ -32957,7 +32958,7 @@
       <c r="BH120" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="BI120" s="4" t="n">
+      <c r="BI120" s="6" t="n">
         <v>45544.44725694445</v>
       </c>
       <c r="BJ120" s="2" t="inlineStr">
@@ -32968,9 +32969,9 @@
       <c r="BK120" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="BL120" s="2" t="inlineStr">
-        <is>
-          <t>7.22833222021807e+18</t>
+      <c r="BL120" s="7" t="inlineStr">
+        <is>
+          <t>07228332220218070015</t>
         </is>
       </c>
       <c r="BM120" s="2" t="inlineStr"/>
@@ -33165,7 +33166,7 @@
       <c r="BI121" s="2" t="inlineStr"/>
       <c r="BJ121" s="2" t="inlineStr"/>
       <c r="BK121" s="2" t="inlineStr"/>
-      <c r="BL121" s="2" t="inlineStr"/>
+      <c r="BL121" s="2" t="n"/>
       <c r="BM121" s="2" t="inlineStr"/>
       <c r="BN121" s="2" t="inlineStr"/>
       <c r="BO121" s="2" t="inlineStr"/>
@@ -33370,7 +33371,7 @@
       <c r="BI122" s="2" t="inlineStr"/>
       <c r="BJ122" s="2" t="inlineStr"/>
       <c r="BK122" s="2" t="inlineStr"/>
-      <c r="BL122" s="2" t="inlineStr"/>
+      <c r="BL122" s="2" t="n"/>
       <c r="BM122" s="2" t="inlineStr"/>
       <c r="BN122" s="2" t="inlineStr"/>
       <c r="BO122" s="2" t="inlineStr"/>
@@ -33647,7 +33648,7 @@
           <t>6 OFICIO DE REG DE IMOVEIS</t>
         </is>
       </c>
-      <c r="BB123" s="4" t="n">
+      <c r="BB123" s="6" t="n">
         <v>41288</v>
       </c>
       <c r="BC123" s="2" t="inlineStr">
@@ -33675,7 +33676,7 @@
       <c r="BK123" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL123" s="2" t="inlineStr"/>
+      <c r="BL123" s="2" t="n"/>
       <c r="BM123" s="2" t="inlineStr"/>
       <c r="BN123" s="2" t="inlineStr"/>
       <c r="BO123" s="2" t="n">
@@ -33954,7 +33955,7 @@
           <t>6 OFICIO DE REG DE IMOVEIS</t>
         </is>
       </c>
-      <c r="BB124" s="4" t="n">
+      <c r="BB124" s="6" t="n">
         <v>41288</v>
       </c>
       <c r="BC124" s="2" t="inlineStr">
@@ -33982,7 +33983,7 @@
       <c r="BK124" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL124" s="2" t="inlineStr"/>
+      <c r="BL124" s="2" t="n"/>
       <c r="BM124" s="2" t="inlineStr"/>
       <c r="BN124" s="2" t="inlineStr"/>
       <c r="BO124" s="2" t="n">
@@ -34261,7 +34262,7 @@
           <t>6 OFICIO DE REG DE IMOVEIS</t>
         </is>
       </c>
-      <c r="BB125" s="4" t="n">
+      <c r="BB125" s="6" t="n">
         <v>41288</v>
       </c>
       <c r="BC125" s="2" t="inlineStr">
@@ -34289,7 +34290,7 @@
       <c r="BK125" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="BL125" s="2" t="inlineStr"/>
+      <c r="BL125" s="2" t="n"/>
       <c r="BM125" s="2" t="inlineStr"/>
       <c r="BN125" s="2" t="inlineStr"/>
       <c r="BO125" s="2" t="n">
@@ -34590,9 +34591,9 @@
       <c r="BK126" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="BL126" s="2" t="inlineStr">
-        <is>
-          <t>7.14110632025807e+18; 7.47126622025807e+18</t>
+      <c r="BL126" s="7" t="inlineStr">
+        <is>
+          <t>07141106320258070018; 07471266220258070000</t>
         </is>
       </c>
       <c r="BM126" s="2" t="inlineStr"/>
@@ -37365,7 +37366,7 @@
       <c r="A2" s="2" t="n">
         <v>14770</v>
       </c>
-      <c r="B2" s="4" t="n">
+      <c r="B2" s="6" t="n">
         <v>40473</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -37378,7 +37379,7 @@
       <c r="A3" s="2" t="n">
         <v>14770</v>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B3" s="6" t="n">
         <v>40506</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -37391,7 +37392,7 @@
       <c r="A4" s="2" t="n">
         <v>14770</v>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B4" s="6" t="n">
         <v>40506.41592592592</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -37404,7 +37405,7 @@
       <c r="A5" s="2" t="n">
         <v>14770</v>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="6" t="n">
         <v>40988</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -37417,7 +37418,7 @@
       <c r="A6" s="2" t="n">
         <v>14770</v>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="6" t="n">
         <v>43510.47511574074</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -37430,7 +37431,7 @@
       <c r="A7" s="2" t="n">
         <v>14770</v>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B7" s="6" t="n">
         <v>44344.40212962963</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -37443,7 +37444,7 @@
       <c r="A8" s="2" t="n">
         <v>14770</v>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B8" s="6" t="n">
         <v>44578.71516203704</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -37456,7 +37457,7 @@
       <c r="A9" s="2" t="n">
         <v>14770</v>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B9" s="6" t="n">
         <v>44585.374375</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -37469,7 +37470,7 @@
       <c r="A10" s="2" t="n">
         <v>14770</v>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B10" s="6" t="n">
         <v>46174.39575231481</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -37482,7 +37483,7 @@
       <c r="A11" s="2" t="n">
         <v>31043</v>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B11" s="6" t="n">
         <v>44327.4975</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -37495,7 +37496,7 @@
       <c r="A12" s="2" t="n">
         <v>31043</v>
       </c>
-      <c r="B12" s="4" t="n">
+      <c r="B12" s="6" t="n">
         <v>45145.86328703703</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -37508,7 +37509,7 @@
       <c r="A13" s="2" t="n">
         <v>31043</v>
       </c>
-      <c r="B13" s="4" t="n">
+      <c r="B13" s="6" t="n">
         <v>45995.92784722222</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -37522,7 +37523,7 @@
       <c r="A14" s="2" t="n">
         <v>31043</v>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="6" t="n">
         <v>46083.42450231482</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -37535,7 +37536,7 @@
       <c r="A15" s="2" t="n">
         <v>54782</v>
       </c>
-      <c r="B15" s="4" t="n">
+      <c r="B15" s="6" t="n">
         <v>35517</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -37548,7 +37549,7 @@
       <c r="A16" s="2" t="n">
         <v>54782</v>
       </c>
-      <c r="B16" s="4" t="n">
+      <c r="B16" s="6" t="n">
         <v>37784</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -37561,7 +37562,7 @@
       <c r="A17" s="2" t="n">
         <v>54782</v>
       </c>
-      <c r="B17" s="4" t="n">
+      <c r="B17" s="6" t="n">
         <v>41960.62563657408</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -37574,7 +37575,7 @@
       <c r="A18" s="2" t="n">
         <v>54782</v>
       </c>
-      <c r="B18" s="4" t="n">
+      <c r="B18" s="6" t="n">
         <v>41988.36842592592</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -37587,7 +37588,7 @@
       <c r="A19" s="2" t="n">
         <v>54782</v>
       </c>
-      <c r="B19" s="4" t="n">
+      <c r="B19" s="6" t="n">
         <v>42881.99998842592</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -37600,7 +37601,7 @@
       <c r="A20" s="2" t="n">
         <v>54782</v>
       </c>
-      <c r="B20" s="4" t="n">
+      <c r="B20" s="6" t="n">
         <v>42991.38122685185</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -37613,7 +37614,7 @@
       <c r="A21" s="2" t="n">
         <v>54782</v>
       </c>
-      <c r="B21" s="4" t="n">
+      <c r="B21" s="6" t="n">
         <v>46209.74333333333</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -37627,7 +37628,7 @@
       <c r="A22" s="2" t="n">
         <v>61182</v>
       </c>
-      <c r="B22" s="4" t="n">
+      <c r="B22" s="6" t="n">
         <v>35517</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -37640,7 +37641,7 @@
       <c r="A23" s="2" t="n">
         <v>61182</v>
       </c>
-      <c r="B23" s="4" t="n">
+      <c r="B23" s="6" t="n">
         <v>42881.99998842592</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -37653,7 +37654,7 @@
       <c r="A24" s="2" t="n">
         <v>61182</v>
       </c>
-      <c r="B24" s="4" t="n">
+      <c r="B24" s="6" t="n">
         <v>42991.38122685185</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -37666,7 +37667,7 @@
       <c r="A25" s="2" t="n">
         <v>62893</v>
       </c>
-      <c r="B25" s="4" t="n">
+      <c r="B25" s="6" t="n">
         <v>35517</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -37679,7 +37680,7 @@
       <c r="A26" s="2" t="n">
         <v>62893</v>
       </c>
-      <c r="B26" s="4" t="n">
+      <c r="B26" s="6" t="n">
         <v>42881.99998842592</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -37692,7 +37693,7 @@
       <c r="A27" s="2" t="n">
         <v>62893</v>
       </c>
-      <c r="B27" s="4" t="n">
+      <c r="B27" s="6" t="n">
         <v>42991.38122685185</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -37705,7 +37706,7 @@
       <c r="A28" s="2" t="n">
         <v>62893</v>
       </c>
-      <c r="B28" s="4" t="n">
+      <c r="B28" s="6" t="n">
         <v>43032.49983796296</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -37718,7 +37719,7 @@
       <c r="A29" s="2" t="n">
         <v>62893</v>
       </c>
-      <c r="B29" s="4" t="n">
+      <c r="B29" s="6" t="n">
         <v>43518.71640046296</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -37731,7 +37732,7 @@
       <c r="A30" s="2" t="n">
         <v>63548</v>
       </c>
-      <c r="B30" s="4" t="n">
+      <c r="B30" s="6" t="n">
         <v>42401.67120370371</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -37744,7 +37745,7 @@
       <c r="A31" s="2" t="n">
         <v>63548</v>
       </c>
-      <c r="B31" s="4" t="n">
+      <c r="B31" s="6" t="n">
         <v>42832.45384259259</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -37757,7 +37758,7 @@
       <c r="A32" s="2" t="n">
         <v>63548</v>
       </c>
-      <c r="B32" s="4" t="n">
+      <c r="B32" s="6" t="n">
         <v>43026.43789351852</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -37770,7 +37771,7 @@
       <c r="A33" s="2" t="n">
         <v>63548</v>
       </c>
-      <c r="B33" s="4" t="n">
+      <c r="B33" s="6" t="n">
         <v>43026.51416666667</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -37783,7 +37784,7 @@
       <c r="A34" s="2" t="n">
         <v>63548</v>
       </c>
-      <c r="B34" s="4" t="n">
+      <c r="B34" s="6" t="n">
         <v>43038.71348379629</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -37796,7 +37797,7 @@
       <c r="A35" s="2" t="n">
         <v>63548</v>
       </c>
-      <c r="B35" s="4" t="n">
+      <c r="B35" s="6" t="n">
         <v>43644.46751157408</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -37810,7 +37811,7 @@
       <c r="A36" s="2" t="n">
         <v>63548</v>
       </c>
-      <c r="B36" s="4" t="n">
+      <c r="B36" s="6" t="n">
         <v>44109.39166666667</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -37823,7 +37824,7 @@
       <c r="A37" s="2" t="n">
         <v>64341</v>
       </c>
-      <c r="B37" s="4" t="n">
+      <c r="B37" s="6" t="n">
         <v>39603</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -37836,7 +37837,7 @@
       <c r="A38" s="2" t="n">
         <v>64341</v>
       </c>
-      <c r="B38" s="4" t="n">
+      <c r="B38" s="6" t="n">
         <v>39609.59695601852</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -37849,7 +37850,7 @@
       <c r="A39" s="2" t="n">
         <v>64341</v>
       </c>
-      <c r="B39" s="4" t="n">
+      <c r="B39" s="6" t="n">
         <v>39755.64422453703</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -37862,7 +37863,7 @@
       <c r="A40" s="2" t="n">
         <v>64341</v>
       </c>
-      <c r="B40" s="4" t="n">
+      <c r="B40" s="6" t="n">
         <v>39895</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -37875,7 +37876,7 @@
       <c r="A41" s="2" t="n">
         <v>64341</v>
       </c>
-      <c r="B41" s="4" t="n">
+      <c r="B41" s="6" t="n">
         <v>39952.68584490741</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -37888,7 +37889,7 @@
       <c r="A42" s="2" t="n">
         <v>64341</v>
       </c>
-      <c r="B42" s="4" t="n">
+      <c r="B42" s="6" t="n">
         <v>40065.64831018518</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -37901,7 +37902,7 @@
       <c r="A43" s="2" t="n">
         <v>64341</v>
       </c>
-      <c r="B43" s="4" t="n">
+      <c r="B43" s="6" t="n">
         <v>40557.61615740741</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -37914,7 +37915,7 @@
       <c r="A44" s="2" t="n">
         <v>64341</v>
       </c>
-      <c r="B44" s="4" t="n">
+      <c r="B44" s="6" t="n">
         <v>41124.39414351852</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -37927,7 +37928,7 @@
       <c r="A45" s="2" t="n">
         <v>64341</v>
       </c>
-      <c r="B45" s="4" t="n">
+      <c r="B45" s="6" t="n">
         <v>41192</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -37940,7 +37941,7 @@
       <c r="A46" s="2" t="n">
         <v>64341</v>
       </c>
-      <c r="B46" s="4" t="n">
+      <c r="B46" s="6" t="n">
         <v>42447.66908564815</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -37953,7 +37954,7 @@
       <c r="A47" s="2" t="n">
         <v>64341</v>
       </c>
-      <c r="B47" s="4" t="n">
+      <c r="B47" s="6" t="n">
         <v>42881.99998842592</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -37966,7 +37967,7 @@
       <c r="A48" s="2" t="n">
         <v>64341</v>
       </c>
-      <c r="B48" s="4" t="n">
+      <c r="B48" s="6" t="n">
         <v>42991.38122685185</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -37979,7 +37980,7 @@
       <c r="A49" s="2" t="n">
         <v>64341</v>
       </c>
-      <c r="B49" s="4" t="n">
+      <c r="B49" s="6" t="n">
         <v>44433.45929398148</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -37992,7 +37993,7 @@
       <c r="A50" s="2" t="n">
         <v>70919</v>
       </c>
-      <c r="B50" s="4" t="n">
+      <c r="B50" s="6" t="n">
         <v>35517</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -38005,7 +38006,7 @@
       <c r="A51" s="2" t="n">
         <v>70919</v>
       </c>
-      <c r="B51" s="4" t="n">
+      <c r="B51" s="6" t="n">
         <v>42881.99998842592</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -38018,7 +38019,7 @@
       <c r="A52" s="2" t="n">
         <v>70919</v>
       </c>
-      <c r="B52" s="4" t="n">
+      <c r="B52" s="6" t="n">
         <v>42991.38122685185</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -38031,7 +38032,7 @@
       <c r="A53" s="2" t="n">
         <v>70919</v>
       </c>
-      <c r="B53" s="4" t="n">
+      <c r="B53" s="6" t="n">
         <v>43921.4324537037</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -38044,7 +38045,7 @@
       <c r="A54" s="2" t="n">
         <v>70919</v>
       </c>
-      <c r="B54" s="4" t="n">
+      <c r="B54" s="6" t="n">
         <v>44342.43344907407</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -38057,7 +38058,7 @@
       <c r="A55" s="2" t="n">
         <v>70919</v>
       </c>
-      <c r="B55" s="4" t="n">
+      <c r="B55" s="6" t="n">
         <v>45294.48045138889</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -38071,7 +38072,7 @@
       <c r="A56" s="2" t="n">
         <v>70919</v>
       </c>
-      <c r="B56" s="4" t="n">
+      <c r="B56" s="6" t="n">
         <v>45352.61450231481</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -38084,7 +38085,7 @@
       <c r="A57" s="2" t="n">
         <v>70919</v>
       </c>
-      <c r="B57" s="4" t="n">
+      <c r="B57" s="6" t="n">
         <v>45467.74733796297</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -38097,7 +38098,7 @@
       <c r="A58" s="2" t="n">
         <v>70919</v>
       </c>
-      <c r="B58" s="4" t="n">
+      <c r="B58" s="6" t="n">
         <v>45691.54793981482</v>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -38110,7 +38111,7 @@
       <c r="A59" s="2" t="n">
         <v>70919</v>
       </c>
-      <c r="B59" s="4" t="n">
+      <c r="B59" s="6" t="n">
         <v>45860.38936342593</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -38123,7 +38124,7 @@
       <c r="A60" s="2" t="n">
         <v>104370</v>
       </c>
-      <c r="B60" s="4" t="n">
+      <c r="B60" s="6" t="n">
         <v>45007.386875</v>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -38136,7 +38137,7 @@
       <c r="A61" s="2" t="n">
         <v>104371</v>
       </c>
-      <c r="B61" s="4" t="n">
+      <c r="B61" s="6" t="n">
         <v>45007.386875</v>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -38149,7 +38150,7 @@
       <c r="A62" s="2" t="n">
         <v>104372</v>
       </c>
-      <c r="B62" s="4" t="n">
+      <c r="B62" s="6" t="n">
         <v>45007.386875</v>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -38162,7 +38163,7 @@
       <c r="A63" s="2" t="n">
         <v>109437</v>
       </c>
-      <c r="B63" s="4" t="n">
+      <c r="B63" s="6" t="n">
         <v>38244</v>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -38175,7 +38176,7 @@
       <c r="A64" s="2" t="n">
         <v>164319</v>
       </c>
-      <c r="B64" s="4" t="n">
+      <c r="B64" s="6" t="n">
         <v>35517</v>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -38188,7 +38189,7 @@
       <c r="A65" s="2" t="n">
         <v>164319</v>
       </c>
-      <c r="B65" s="4" t="n">
+      <c r="B65" s="6" t="n">
         <v>44775.48605324074</v>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -38201,7 +38202,7 @@
       <c r="A66" s="2" t="n">
         <v>164319</v>
       </c>
-      <c r="B66" s="4" t="n">
+      <c r="B66" s="6" t="n">
         <v>44782.42739583334</v>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -38214,7 +38215,7 @@
       <c r="A67" s="2" t="n">
         <v>164319</v>
       </c>
-      <c r="B67" s="4" t="n">
+      <c r="B67" s="6" t="n">
         <v>45544.44724537037</v>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -38227,7 +38228,7 @@
       <c r="A68" s="2" t="n">
         <v>164320</v>
       </c>
-      <c r="B68" s="4" t="n">
+      <c r="B68" s="6" t="n">
         <v>35517</v>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -38240,7 +38241,7 @@
       <c r="A69" s="2" t="n">
         <v>164320</v>
       </c>
-      <c r="B69" s="4" t="n">
+      <c r="B69" s="6" t="n">
         <v>44775.48605324074</v>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -38253,7 +38254,7 @@
       <c r="A70" s="2" t="n">
         <v>164320</v>
       </c>
-      <c r="B70" s="4" t="n">
+      <c r="B70" s="6" t="n">
         <v>44782.42762731481</v>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -38266,7 +38267,7 @@
       <c r="A71" s="2" t="n">
         <v>164320</v>
       </c>
-      <c r="B71" s="4" t="n">
+      <c r="B71" s="6" t="n">
         <v>45544.44725694445</v>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -38279,7 +38280,7 @@
       <c r="A72" s="2" t="n">
         <v>164325</v>
       </c>
-      <c r="B72" s="4" t="n">
+      <c r="B72" s="6" t="n">
         <v>35517</v>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -38292,7 +38293,7 @@
       <c r="A73" s="2" t="n">
         <v>164326</v>
       </c>
-      <c r="B73" s="4" t="n">
+      <c r="B73" s="6" t="n">
         <v>35517</v>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -38305,7 +38306,7 @@
       <c r="A74" s="2" t="n">
         <v>164327</v>
       </c>
-      <c r="B74" s="4" t="n">
+      <c r="B74" s="6" t="n">
         <v>35517</v>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -38318,7 +38319,7 @@
       <c r="A75" s="2" t="n">
         <v>211948</v>
       </c>
-      <c r="B75" s="4" t="n">
+      <c r="B75" s="6" t="n">
         <v>36147</v>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -38331,7 +38332,7 @@
       <c r="A76" s="2" t="n">
         <v>211948</v>
       </c>
-      <c r="B76" s="4" t="n">
+      <c r="B76" s="6" t="n">
         <v>41269</v>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -38344,7 +38345,7 @@
       <c r="A77" s="2" t="n">
         <v>211948</v>
       </c>
-      <c r="B77" s="4" t="n">
+      <c r="B77" s="6" t="n">
         <v>41389.44746527778</v>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -38357,7 +38358,7 @@
       <c r="A78" s="2" t="n">
         <v>211948</v>
       </c>
-      <c r="B78" s="4" t="n">
+      <c r="B78" s="6" t="n">
         <v>41397.66862268518</v>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -38370,7 +38371,7 @@
       <c r="A79" s="2" t="n">
         <v>211948</v>
       </c>
-      <c r="B79" s="4" t="n">
+      <c r="B79" s="6" t="n">
         <v>41918.58230324074</v>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -38383,7 +38384,7 @@
       <c r="A80" s="2" t="n">
         <v>211948</v>
       </c>
-      <c r="B80" s="4" t="n">
+      <c r="B80" s="6" t="n">
         <v>42096.62530092592</v>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -38396,7 +38397,7 @@
       <c r="A81" s="2" t="n">
         <v>211948</v>
       </c>
-      <c r="B81" s="4" t="n">
+      <c r="B81" s="6" t="n">
         <v>42881.99998842592</v>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -38409,7 +38410,7 @@
       <c r="A82" s="2" t="n">
         <v>211948</v>
       </c>
-      <c r="B82" s="4" t="n">
+      <c r="B82" s="6" t="n">
         <v>42895.41425925926</v>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -38422,7 +38423,7 @@
       <c r="A83" s="2" t="n">
         <v>211948</v>
       </c>
-      <c r="B83" s="4" t="n">
+      <c r="B83" s="6" t="n">
         <v>42991.38122685185</v>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -38435,7 +38436,7 @@
       <c r="A84" s="2" t="n">
         <v>211948</v>
       </c>
-      <c r="B84" s="4" t="n">
+      <c r="B84" s="6" t="n">
         <v>44760.65194444444</v>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -38448,7 +38449,7 @@
       <c r="A85" s="2" t="n">
         <v>211948</v>
       </c>
-      <c r="B85" s="4" t="n">
+      <c r="B85" s="6" t="n">
         <v>44845.75594907408</v>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -38461,7 +38462,7 @@
       <c r="A86" s="2" t="n">
         <v>212548</v>
       </c>
-      <c r="B86" s="4" t="n">
+      <c r="B86" s="6" t="n">
         <v>37519</v>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -38474,7 +38475,7 @@
       <c r="A87" s="2" t="n">
         <v>212548</v>
       </c>
-      <c r="B87" s="4" t="n">
+      <c r="B87" s="6" t="n">
         <v>41400.73694444444</v>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -38487,7 +38488,7 @@
       <c r="A88" s="2" t="n">
         <v>212548</v>
       </c>
-      <c r="B88" s="4" t="n">
+      <c r="B88" s="6" t="n">
         <v>42881.99998842592</v>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -38500,7 +38501,7 @@
       <c r="A89" s="2" t="n">
         <v>212548</v>
       </c>
-      <c r="B89" s="4" t="n">
+      <c r="B89" s="6" t="n">
         <v>42991.38122685185</v>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -38513,7 +38514,7 @@
       <c r="A90" s="2" t="n">
         <v>212548</v>
       </c>
-      <c r="B90" s="4" t="n">
+      <c r="B90" s="6" t="n">
         <v>46164.41681712963</v>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -38526,7 +38527,7 @@
       <c r="A91" s="2" t="n">
         <v>212548</v>
       </c>
-      <c r="B91" s="4" t="n">
+      <c r="B91" s="6" t="n">
         <v>46174.41376157408</v>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -38539,7 +38540,7 @@
       <c r="A92" s="2" t="n">
         <v>212548</v>
       </c>
-      <c r="B92" s="4" t="n">
+      <c r="B92" s="6" t="n">
         <v>46206.56833333334</v>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -38552,7 +38553,7 @@
       <c r="A93" s="2" t="n">
         <v>492096</v>
       </c>
-      <c r="B93" s="4" t="n">
+      <c r="B93" s="6" t="n">
         <v>36741</v>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -38565,7 +38566,7 @@
       <c r="A94" s="2" t="n">
         <v>492096</v>
       </c>
-      <c r="B94" s="4" t="n">
+      <c r="B94" s="6" t="n">
         <v>42276.46481481481</v>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -38578,7 +38579,7 @@
       <c r="A95" s="2" t="n">
         <v>492096</v>
       </c>
-      <c r="B95" s="4" t="n">
+      <c r="B95" s="6" t="n">
         <v>42276.65513888889</v>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -38591,7 +38592,7 @@
       <c r="A96" s="2" t="n">
         <v>492096</v>
       </c>
-      <c r="B96" s="4" t="n">
+      <c r="B96" s="6" t="n">
         <v>42675.56388888889</v>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -38604,7 +38605,7 @@
       <c r="A97" s="2" t="n">
         <v>492096</v>
       </c>
-      <c r="B97" s="4" t="n">
+      <c r="B97" s="6" t="n">
         <v>42881.99998842592</v>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -38617,7 +38618,7 @@
       <c r="A98" s="2" t="n">
         <v>492096</v>
       </c>
-      <c r="B98" s="4" t="n">
+      <c r="B98" s="6" t="n">
         <v>42991.38122685185</v>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -38630,7 +38631,7 @@
       <c r="A99" s="2" t="n">
         <v>492096</v>
       </c>
-      <c r="B99" s="4" t="n">
+      <c r="B99" s="6" t="n">
         <v>43721.61274305556</v>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -38643,7 +38644,7 @@
       <c r="A100" s="2" t="n">
         <v>523843</v>
       </c>
-      <c r="B100" s="4" t="n">
+      <c r="B100" s="6" t="n">
         <v>39826.68127314815</v>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -38656,7 +38657,7 @@
       <c r="A101" s="2" t="n">
         <v>523843</v>
       </c>
-      <c r="B101" s="4" t="n">
+      <c r="B101" s="6" t="n">
         <v>41684.44163194444</v>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -38669,7 +38670,7 @@
       <c r="A102" s="2" t="n">
         <v>523843</v>
       </c>
-      <c r="B102" s="4" t="n">
+      <c r="B102" s="6" t="n">
         <v>42025.38631944444</v>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -38682,7 +38683,7 @@
       <c r="A103" s="2" t="n">
         <v>523843</v>
       </c>
-      <c r="B103" s="4" t="n">
+      <c r="B103" s="6" t="n">
         <v>42762.44840277778</v>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -38695,7 +38696,7 @@
       <c r="A104" s="2" t="n">
         <v>523843</v>
       </c>
-      <c r="B104" s="4" t="n">
+      <c r="B104" s="6" t="n">
         <v>42881.99998842592</v>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -38708,7 +38709,7 @@
       <c r="A105" s="2" t="n">
         <v>523843</v>
       </c>
-      <c r="B105" s="4" t="n">
+      <c r="B105" s="6" t="n">
         <v>42991.38122685185</v>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -38721,7 +38722,7 @@
       <c r="A106" s="2" t="n">
         <v>523843</v>
       </c>
-      <c r="B106" s="4" t="n">
+      <c r="B106" s="6" t="n">
         <v>43657.63366898148</v>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -38734,7 +38735,7 @@
       <c r="A107" s="2" t="n">
         <v>523843</v>
       </c>
-      <c r="B107" s="4" t="n">
+      <c r="B107" s="6" t="n">
         <v>43754.39363425926</v>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -38747,7 +38748,7 @@
       <c r="A108" s="2" t="n">
         <v>523843</v>
       </c>
-      <c r="B108" s="4" t="n">
+      <c r="B108" s="6" t="n">
         <v>45868.46273148148</v>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -38760,7 +38761,7 @@
       <c r="A109" s="2" t="n">
         <v>523844</v>
       </c>
-      <c r="B109" s="4" t="n">
+      <c r="B109" s="6" t="n">
         <v>39826.68127314815</v>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -38773,7 +38774,7 @@
       <c r="A110" s="2" t="n">
         <v>523844</v>
       </c>
-      <c r="B110" s="4" t="n">
+      <c r="B110" s="6" t="n">
         <v>41684.44163194444</v>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -38786,7 +38787,7 @@
       <c r="A111" s="2" t="n">
         <v>523844</v>
       </c>
-      <c r="B111" s="4" t="n">
+      <c r="B111" s="6" t="n">
         <v>42025.38631944444</v>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -38799,7 +38800,7 @@
       <c r="A112" s="2" t="n">
         <v>523844</v>
       </c>
-      <c r="B112" s="4" t="n">
+      <c r="B112" s="6" t="n">
         <v>42762.44840277778</v>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -38812,7 +38813,7 @@
       <c r="A113" s="2" t="n">
         <v>523844</v>
       </c>
-      <c r="B113" s="4" t="n">
+      <c r="B113" s="6" t="n">
         <v>42881.99998842592</v>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -38825,7 +38826,7 @@
       <c r="A114" s="2" t="n">
         <v>523844</v>
       </c>
-      <c r="B114" s="4" t="n">
+      <c r="B114" s="6" t="n">
         <v>42991.38122685185</v>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -38838,7 +38839,7 @@
       <c r="A115" s="2" t="n">
         <v>523844</v>
       </c>
-      <c r="B115" s="4" t="n">
+      <c r="B115" s="6" t="n">
         <v>43657.63366898148</v>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -38851,7 +38852,7 @@
       <c r="A116" s="2" t="n">
         <v>523844</v>
       </c>
-      <c r="B116" s="4" t="n">
+      <c r="B116" s="6" t="n">
         <v>43754.39399305556</v>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -38864,7 +38865,7 @@
       <c r="A117" s="2" t="n">
         <v>523844</v>
       </c>
-      <c r="B117" s="4" t="n">
+      <c r="B117" s="6" t="n">
         <v>45868.46821759259</v>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -38877,7 +38878,7 @@
       <c r="A118" s="2" t="n">
         <v>523845</v>
       </c>
-      <c r="B118" s="4" t="n">
+      <c r="B118" s="6" t="n">
         <v>39749</v>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -38890,7 +38891,7 @@
       <c r="A119" s="2" t="n">
         <v>523845</v>
       </c>
-      <c r="B119" s="4" t="n">
+      <c r="B119" s="6" t="n">
         <v>41684.44163194444</v>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -38903,7 +38904,7 @@
       <c r="A120" s="2" t="n">
         <v>523845</v>
       </c>
-      <c r="B120" s="4" t="n">
+      <c r="B120" s="6" t="n">
         <v>42025.38631944444</v>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -38916,7 +38917,7 @@
       <c r="A121" s="2" t="n">
         <v>523845</v>
       </c>
-      <c r="B121" s="4" t="n">
+      <c r="B121" s="6" t="n">
         <v>42401.57300925926</v>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -38929,7 +38930,7 @@
       <c r="A122" s="2" t="n">
         <v>523845</v>
       </c>
-      <c r="B122" s="4" t="n">
+      <c r="B122" s="6" t="n">
         <v>42881.99998842592</v>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -38942,7 +38943,7 @@
       <c r="A123" s="2" t="n">
         <v>523845</v>
       </c>
-      <c r="B123" s="4" t="n">
+      <c r="B123" s="6" t="n">
         <v>42991.38122685185</v>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -38955,7 +38956,7 @@
       <c r="A124" s="2" t="n">
         <v>523845</v>
       </c>
-      <c r="B124" s="4" t="n">
+      <c r="B124" s="6" t="n">
         <v>43657.63366898148</v>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -38968,7 +38969,7 @@
       <c r="A125" s="2" t="n">
         <v>523845</v>
       </c>
-      <c r="B125" s="4" t="n">
+      <c r="B125" s="6" t="n">
         <v>43754.39328703703</v>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -38981,7 +38982,7 @@
       <c r="A126" s="2" t="n">
         <v>523845</v>
       </c>
-      <c r="B126" s="4" t="n">
+      <c r="B126" s="6" t="n">
         <v>45868.45605324074</v>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -38994,7 +38995,7 @@
       <c r="A127" s="2" t="n">
         <v>523846</v>
       </c>
-      <c r="B127" s="4" t="n">
+      <c r="B127" s="6" t="n">
         <v>39826.68127314815</v>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -39007,7 +39008,7 @@
       <c r="A128" s="2" t="n">
         <v>523846</v>
       </c>
-      <c r="B128" s="4" t="n">
+      <c r="B128" s="6" t="n">
         <v>41684.44163194444</v>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -39020,7 +39021,7 @@
       <c r="A129" s="2" t="n">
         <v>523846</v>
       </c>
-      <c r="B129" s="4" t="n">
+      <c r="B129" s="6" t="n">
         <v>42025.38631944444</v>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -39033,7 +39034,7 @@
       <c r="A130" s="2" t="n">
         <v>523846</v>
       </c>
-      <c r="B130" s="4" t="n">
+      <c r="B130" s="6" t="n">
         <v>42762.44840277778</v>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -39046,7 +39047,7 @@
       <c r="A131" s="2" t="n">
         <v>523846</v>
       </c>
-      <c r="B131" s="4" t="n">
+      <c r="B131" s="6" t="n">
         <v>42881.99998842592</v>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -39059,7 +39060,7 @@
       <c r="A132" s="2" t="n">
         <v>523846</v>
       </c>
-      <c r="B132" s="4" t="n">
+      <c r="B132" s="6" t="n">
         <v>42991.38122685185</v>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -39072,7 +39073,7 @@
       <c r="A133" s="2" t="n">
         <v>523846</v>
       </c>
-      <c r="B133" s="4" t="n">
+      <c r="B133" s="6" t="n">
         <v>43657.63366898148</v>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -39085,7 +39086,7 @@
       <c r="A134" s="2" t="n">
         <v>523846</v>
       </c>
-      <c r="B134" s="4" t="n">
+      <c r="B134" s="6" t="n">
         <v>43754.39435185185</v>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -39098,7 +39099,7 @@
       <c r="A135" s="2" t="n">
         <v>523846</v>
       </c>
-      <c r="B135" s="4" t="n">
+      <c r="B135" s="6" t="n">
         <v>45868.4741087963</v>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -39111,7 +39112,7 @@
       <c r="A136" s="2" t="n">
         <v>523849</v>
       </c>
-      <c r="B136" s="4" t="n">
+      <c r="B136" s="6" t="n">
         <v>42025.38631944444</v>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -39124,7 +39125,7 @@
       <c r="A137" s="2" t="n">
         <v>523849</v>
       </c>
-      <c r="B137" s="4" t="n">
+      <c r="B137" s="6" t="n">
         <v>42881.99998842592</v>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -39137,7 +39138,7 @@
       <c r="A138" s="2" t="n">
         <v>523849</v>
       </c>
-      <c r="B138" s="4" t="n">
+      <c r="B138" s="6" t="n">
         <v>42991.38122685185</v>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -39150,7 +39151,7 @@
       <c r="A139" s="2" t="n">
         <v>523854</v>
       </c>
-      <c r="B139" s="4" t="n">
+      <c r="B139" s="6" t="n">
         <v>37698</v>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -39164,7 +39165,7 @@
       <c r="A140" s="2" t="n">
         <v>523854</v>
       </c>
-      <c r="B140" s="4" t="n">
+      <c r="B140" s="6" t="n">
         <v>41743.60722222222</v>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -39177,7 +39178,7 @@
       <c r="A141" s="2" t="n">
         <v>523854</v>
       </c>
-      <c r="B141" s="4" t="n">
+      <c r="B141" s="6" t="n">
         <v>42025.38631944444</v>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -39190,7 +39191,7 @@
       <c r="A142" s="2" t="n">
         <v>523854</v>
       </c>
-      <c r="B142" s="4" t="n">
+      <c r="B142" s="6" t="n">
         <v>42881.99998842592</v>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -39203,7 +39204,7 @@
       <c r="A143" s="2" t="n">
         <v>523854</v>
       </c>
-      <c r="B143" s="4" t="n">
+      <c r="B143" s="6" t="n">
         <v>42991.38122685185</v>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -39216,7 +39217,7 @@
       <c r="A144" s="2" t="n">
         <v>523856</v>
       </c>
-      <c r="B144" s="4" t="n">
+      <c r="B144" s="6" t="n">
         <v>42025.38631944444</v>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -39229,7 +39230,7 @@
       <c r="A145" s="2" t="n">
         <v>523860</v>
       </c>
-      <c r="B145" s="4" t="n">
+      <c r="B145" s="6" t="n">
         <v>37698</v>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -39242,7 +39243,7 @@
       <c r="A146" s="2" t="n">
         <v>523860</v>
       </c>
-      <c r="B146" s="4" t="n">
+      <c r="B146" s="6" t="n">
         <v>37806</v>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -39255,7 +39256,7 @@
       <c r="A147" s="2" t="n">
         <v>523860</v>
       </c>
-      <c r="B147" s="4" t="n">
+      <c r="B147" s="6" t="n">
         <v>41164.36961805556</v>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -39268,7 +39269,7 @@
       <c r="A148" s="2" t="n">
         <v>523860</v>
       </c>
-      <c r="B148" s="4" t="n">
+      <c r="B148" s="6" t="n">
         <v>42025.38631944444</v>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -39281,7 +39282,7 @@
       <c r="A149" s="2" t="n">
         <v>523860</v>
       </c>
-      <c r="B149" s="4" t="n">
+      <c r="B149" s="6" t="n">
         <v>42401.62921296297</v>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -39294,7 +39295,7 @@
       <c r="A150" s="2" t="n">
         <v>523860</v>
       </c>
-      <c r="B150" s="4" t="n">
+      <c r="B150" s="6" t="n">
         <v>42832.47930555556</v>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -39307,7 +39308,7 @@
       <c r="A151" s="2" t="n">
         <v>523860</v>
       </c>
-      <c r="B151" s="4" t="n">
+      <c r="B151" s="6" t="n">
         <v>43026.49534722222</v>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -39320,7 +39321,7 @@
       <c r="A152" s="2" t="n">
         <v>523860</v>
       </c>
-      <c r="B152" s="4" t="n">
+      <c r="B152" s="6" t="n">
         <v>43026.51416666667</v>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -39333,7 +39334,7 @@
       <c r="A153" s="2" t="n">
         <v>523860</v>
       </c>
-      <c r="B153" s="4" t="n">
+      <c r="B153" s="6" t="n">
         <v>43038.71349537037</v>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -39346,7 +39347,7 @@
       <c r="A154" s="2" t="n">
         <v>523866</v>
       </c>
-      <c r="B154" s="4" t="n">
+      <c r="B154" s="6" t="n">
         <v>37698</v>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -39360,7 +39361,7 @@
       <c r="A155" s="2" t="n">
         <v>523866</v>
       </c>
-      <c r="B155" s="4" t="n">
+      <c r="B155" s="6" t="n">
         <v>42025.38631944444</v>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -39373,7 +39374,7 @@
       <c r="A156" s="2" t="n">
         <v>523866</v>
       </c>
-      <c r="B156" s="4" t="n">
+      <c r="B156" s="6" t="n">
         <v>42881.99998842592</v>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -39386,7 +39387,7 @@
       <c r="A157" s="2" t="n">
         <v>523866</v>
       </c>
-      <c r="B157" s="4" t="n">
+      <c r="B157" s="6" t="n">
         <v>42991.38122685185</v>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -39399,7 +39400,7 @@
       <c r="A158" s="2" t="n">
         <v>523866</v>
       </c>
-      <c r="B158" s="4" t="n">
+      <c r="B158" s="6" t="n">
         <v>43830.47939814815</v>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -39412,7 +39413,7 @@
       <c r="A159" s="2" t="n">
         <v>523866</v>
       </c>
-      <c r="B159" s="4" t="n">
+      <c r="B159" s="6" t="n">
         <v>45995.40071759259</v>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -39425,7 +39426,7 @@
       <c r="A160" s="2" t="n">
         <v>593604</v>
       </c>
-      <c r="B160" s="4" t="n">
+      <c r="B160" s="6" t="n">
         <v>40050.39335648148</v>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -39438,7 +39439,7 @@
       <c r="A161" s="2" t="n">
         <v>593604</v>
       </c>
-      <c r="B161" s="4" t="n">
+      <c r="B161" s="6" t="n">
         <v>40455.71310185185</v>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -39451,7 +39452,7 @@
       <c r="A162" s="2" t="n">
         <v>593604</v>
       </c>
-      <c r="B162" s="4" t="n">
+      <c r="B162" s="6" t="n">
         <v>40735</v>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -39464,7 +39465,7 @@
       <c r="A163" s="2" t="n">
         <v>593604</v>
       </c>
-      <c r="B163" s="4" t="n">
+      <c r="B163" s="6" t="n">
         <v>41558.6830787037</v>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -39477,7 +39478,7 @@
       <c r="A164" s="2" t="n">
         <v>593604</v>
       </c>
-      <c r="B164" s="4" t="n">
+      <c r="B164" s="6" t="n">
         <v>41605.66436342592</v>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -39490,7 +39491,7 @@
       <c r="A165" s="2" t="n">
         <v>593604</v>
       </c>
-      <c r="B165" s="4" t="n">
+      <c r="B165" s="6" t="n">
         <v>42881.99998842592</v>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -39503,7 +39504,7 @@
       <c r="A166" s="2" t="n">
         <v>593604</v>
       </c>
-      <c r="B166" s="4" t="n">
+      <c r="B166" s="6" t="n">
         <v>42991.38122685185</v>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -39516,7 +39517,7 @@
       <c r="A167" s="2" t="n">
         <v>593607</v>
       </c>
-      <c r="B167" s="4" t="n">
+      <c r="B167" s="6" t="n">
         <v>40050.39335648148</v>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -39529,7 +39530,7 @@
       <c r="A168" s="2" t="n">
         <v>593607</v>
       </c>
-      <c r="B168" s="4" t="n">
+      <c r="B168" s="6" t="n">
         <v>40134.49123842592</v>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -39542,7 +39543,7 @@
       <c r="A169" s="2" t="n">
         <v>593607</v>
       </c>
-      <c r="B169" s="4" t="n">
+      <c r="B169" s="6" t="n">
         <v>40437.71325231482</v>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -39555,7 +39556,7 @@
       <c r="A170" s="2" t="n">
         <v>593607</v>
       </c>
-      <c r="B170" s="4" t="n">
+      <c r="B170" s="6" t="n">
         <v>40456.38041666667</v>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -39568,7 +39569,7 @@
       <c r="A171" s="2" t="n">
         <v>593607</v>
       </c>
-      <c r="B171" s="4" t="n">
+      <c r="B171" s="6" t="n">
         <v>40571</v>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -39581,7 +39582,7 @@
       <c r="A172" s="2" t="n">
         <v>593607</v>
       </c>
-      <c r="B172" s="4" t="n">
+      <c r="B172" s="6" t="n">
         <v>40735</v>
       </c>
       <c r="C172" s="2" t="inlineStr">
@@ -39594,7 +39595,7 @@
       <c r="A173" s="2" t="n">
         <v>593607</v>
       </c>
-      <c r="B173" s="4" t="n">
+      <c r="B173" s="6" t="n">
         <v>41900.41920138889</v>
       </c>
       <c r="C173" s="2" t="inlineStr">
@@ -39607,7 +39608,7 @@
       <c r="A174" s="2" t="n">
         <v>593607</v>
       </c>
-      <c r="B174" s="4" t="n">
+      <c r="B174" s="6" t="n">
         <v>41900.59909722222</v>
       </c>
       <c r="C174" s="2" t="inlineStr">
@@ -39620,7 +39621,7 @@
       <c r="A175" s="2" t="n">
         <v>593607</v>
       </c>
-      <c r="B175" s="4" t="n">
+      <c r="B175" s="6" t="n">
         <v>42164.60039351852</v>
       </c>
       <c r="C175" s="2" t="inlineStr">
@@ -39633,7 +39634,7 @@
       <c r="A176" s="2" t="n">
         <v>593607</v>
       </c>
-      <c r="B176" s="4" t="n">
+      <c r="B176" s="6" t="n">
         <v>42881.99998842592</v>
       </c>
       <c r="C176" s="2" t="inlineStr">
@@ -39646,7 +39647,7 @@
       <c r="A177" s="2" t="n">
         <v>593607</v>
       </c>
-      <c r="B177" s="4" t="n">
+      <c r="B177" s="6" t="n">
         <v>42935.77020833334</v>
       </c>
       <c r="C177" s="2" t="inlineStr">
@@ -39659,7 +39660,7 @@
       <c r="A178" s="2" t="n">
         <v>593607</v>
       </c>
-      <c r="B178" s="4" t="n">
+      <c r="B178" s="6" t="n">
         <v>42991.38122685185</v>
       </c>
       <c r="C178" s="2" t="inlineStr">
@@ -39672,7 +39673,7 @@
       <c r="A179" s="2" t="n">
         <v>593607</v>
       </c>
-      <c r="B179" s="4" t="n">
+      <c r="B179" s="6" t="n">
         <v>43962.41179398148</v>
       </c>
       <c r="C179" s="2" t="inlineStr">
@@ -39686,7 +39687,7 @@
       <c r="A180" s="2" t="n">
         <v>593716</v>
       </c>
-      <c r="B180" s="4" t="n">
+      <c r="B180" s="6" t="n">
         <v>40051.38265046296</v>
       </c>
       <c r="C180" s="2" t="inlineStr">
@@ -39699,7 +39700,7 @@
       <c r="A181" s="2" t="n">
         <v>593716</v>
       </c>
-      <c r="B181" s="4" t="n">
+      <c r="B181" s="6" t="n">
         <v>40532</v>
       </c>
       <c r="C181" s="2" t="inlineStr">
@@ -39712,7 +39713,7 @@
       <c r="A182" s="2" t="n">
         <v>593716</v>
       </c>
-      <c r="B182" s="4" t="n">
+      <c r="B182" s="6" t="n">
         <v>40532.71087962963</v>
       </c>
       <c r="C182" s="2" t="inlineStr">
@@ -39725,7 +39726,7 @@
       <c r="A183" s="2" t="n">
         <v>593716</v>
       </c>
-      <c r="B183" s="4" t="n">
+      <c r="B183" s="6" t="n">
         <v>40597</v>
       </c>
       <c r="C183" s="2" t="inlineStr">
@@ -39738,7 +39739,7 @@
       <c r="A184" s="2" t="n">
         <v>593716</v>
       </c>
-      <c r="B184" s="4" t="n">
+      <c r="B184" s="6" t="n">
         <v>40735</v>
       </c>
       <c r="C184" s="2" t="inlineStr">
@@ -39751,7 +39752,7 @@
       <c r="A185" s="2" t="n">
         <v>593716</v>
       </c>
-      <c r="B185" s="4" t="n">
+      <c r="B185" s="6" t="n">
         <v>42775.498125</v>
       </c>
       <c r="C185" s="2" t="inlineStr">
@@ -39764,7 +39765,7 @@
       <c r="A186" s="2" t="n">
         <v>593716</v>
       </c>
-      <c r="B186" s="4" t="n">
+      <c r="B186" s="6" t="n">
         <v>42779.73387731481</v>
       </c>
       <c r="C186" s="2" t="inlineStr">
@@ -39777,7 +39778,7 @@
       <c r="A187" s="2" t="n">
         <v>593716</v>
       </c>
-      <c r="B187" s="4" t="n">
+      <c r="B187" s="6" t="n">
         <v>42881.99998842592</v>
       </c>
       <c r="C187" s="2" t="inlineStr">
@@ -39790,7 +39791,7 @@
       <c r="A188" s="2" t="n">
         <v>593716</v>
       </c>
-      <c r="B188" s="4" t="n">
+      <c r="B188" s="6" t="n">
         <v>42991.38122685185</v>
       </c>
       <c r="C188" s="2" t="inlineStr">
@@ -39803,7 +39804,7 @@
       <c r="A189" s="2" t="n">
         <v>593716</v>
       </c>
-      <c r="B189" s="4" t="n">
+      <c r="B189" s="6" t="n">
         <v>43609.62621527778</v>
       </c>
       <c r="C189" s="2" t="inlineStr">
@@ -39816,7 +39817,7 @@
       <c r="A190" s="2" t="n">
         <v>593716</v>
       </c>
-      <c r="B190" s="4" t="n">
+      <c r="B190" s="6" t="n">
         <v>45617.46763888889</v>
       </c>
       <c r="C190" s="2" t="inlineStr">
@@ -39829,7 +39830,7 @@
       <c r="A191" s="2" t="n">
         <v>593716</v>
       </c>
-      <c r="B191" s="4" t="n">
+      <c r="B191" s="6" t="n">
         <v>45653.57881944445</v>
       </c>
       <c r="C191" s="2" t="inlineStr">
@@ -39842,7 +39843,7 @@
       <c r="A192" s="2" t="n">
         <v>593725</v>
       </c>
-      <c r="B192" s="4" t="n">
+      <c r="B192" s="6" t="n">
         <v>40050.39335648148</v>
       </c>
       <c r="C192" s="2" t="inlineStr">
@@ -39855,7 +39856,7 @@
       <c r="A193" s="2" t="n">
         <v>593725</v>
       </c>
-      <c r="B193" s="4" t="n">
+      <c r="B193" s="6" t="n">
         <v>40522.41050925926</v>
       </c>
       <c r="C193" s="2" t="inlineStr">
@@ -39868,7 +39869,7 @@
       <c r="A194" s="2" t="n">
         <v>593725</v>
       </c>
-      <c r="B194" s="4" t="n">
+      <c r="B194" s="6" t="n">
         <v>40735</v>
       </c>
       <c r="C194" s="2" t="inlineStr">
@@ -39881,7 +39882,7 @@
       <c r="A195" s="2" t="n">
         <v>593725</v>
       </c>
-      <c r="B195" s="4" t="n">
+      <c r="B195" s="6" t="n">
         <v>42783.3704050926</v>
       </c>
       <c r="C195" s="2" t="inlineStr">
@@ -39894,7 +39895,7 @@
       <c r="A196" s="2" t="n">
         <v>593725</v>
       </c>
-      <c r="B196" s="4" t="n">
+      <c r="B196" s="6" t="n">
         <v>42788.52245370371</v>
       </c>
       <c r="C196" s="2" t="inlineStr">
@@ -39907,7 +39908,7 @@
       <c r="A197" s="2" t="n">
         <v>593725</v>
       </c>
-      <c r="B197" s="4" t="n">
+      <c r="B197" s="6" t="n">
         <v>42881.99998842592</v>
       </c>
       <c r="C197" s="2" t="inlineStr">
@@ -39920,7 +39921,7 @@
       <c r="A198" s="2" t="n">
         <v>593725</v>
       </c>
-      <c r="B198" s="4" t="n">
+      <c r="B198" s="6" t="n">
         <v>42991.38122685185</v>
       </c>
       <c r="C198" s="2" t="inlineStr">
@@ -39933,7 +39934,7 @@
       <c r="A199" s="2" t="n">
         <v>593725</v>
       </c>
-      <c r="B199" s="4" t="n">
+      <c r="B199" s="6" t="n">
         <v>43592.63320601852</v>
       </c>
       <c r="C199" s="2" t="inlineStr">
@@ -39946,7 +39947,7 @@
       <c r="A200" s="2" t="n">
         <v>593725</v>
       </c>
-      <c r="B200" s="4" t="n">
+      <c r="B200" s="6" t="n">
         <v>43727.668125</v>
       </c>
       <c r="C200" s="2" t="inlineStr">
@@ -39959,7 +39960,7 @@
       <c r="A201" s="2" t="n">
         <v>593725</v>
       </c>
-      <c r="B201" s="4" t="n">
+      <c r="B201" s="6" t="n">
         <v>45315.50809027778</v>
       </c>
       <c r="C201" s="2" t="inlineStr">
@@ -39972,7 +39973,7 @@
       <c r="A202" s="2" t="n">
         <v>593880</v>
       </c>
-      <c r="B202" s="4" t="n">
+      <c r="B202" s="6" t="n">
         <v>40050.39335648148</v>
       </c>
       <c r="C202" s="2" t="inlineStr">
@@ -39985,7 +39986,7 @@
       <c r="A203" s="2" t="n">
         <v>593880</v>
       </c>
-      <c r="B203" s="4" t="n">
+      <c r="B203" s="6" t="n">
         <v>40493.67197916667</v>
       </c>
       <c r="C203" s="2" t="inlineStr">
@@ -39998,7 +39999,7 @@
       <c r="A204" s="2" t="n">
         <v>593880</v>
       </c>
-      <c r="B204" s="4" t="n">
+      <c r="B204" s="6" t="n">
         <v>40584</v>
       </c>
       <c r="C204" s="2" t="inlineStr">
@@ -40011,7 +40012,7 @@
       <c r="A205" s="2" t="n">
         <v>593880</v>
       </c>
-      <c r="B205" s="4" t="n">
+      <c r="B205" s="6" t="n">
         <v>42375.48560185185</v>
       </c>
       <c r="C205" s="2" t="inlineStr">
@@ -40024,7 +40025,7 @@
       <c r="A206" s="2" t="n">
         <v>593880</v>
       </c>
-      <c r="B206" s="4" t="n">
+      <c r="B206" s="6" t="n">
         <v>43612.67246527778</v>
       </c>
       <c r="C206" s="2" t="inlineStr">
@@ -40037,7 +40038,7 @@
       <c r="A207" s="2" t="n">
         <v>593880</v>
       </c>
-      <c r="B207" s="4" t="n">
+      <c r="B207" s="6" t="n">
         <v>43612.67310185185</v>
       </c>
       <c r="C207" s="2" t="inlineStr">
@@ -40050,7 +40051,7 @@
       <c r="A208" s="2" t="n">
         <v>593880</v>
       </c>
-      <c r="B208" s="4" t="n">
+      <c r="B208" s="6" t="n">
         <v>43613.50334490741</v>
       </c>
       <c r="C208" s="2" t="inlineStr">
@@ -40063,7 +40064,7 @@
       <c r="A209" s="2" t="n">
         <v>593880</v>
       </c>
-      <c r="B209" s="4" t="n">
+      <c r="B209" s="6" t="n">
         <v>43613.72193287037</v>
       </c>
       <c r="C209" s="2" t="inlineStr">
@@ -40076,7 +40077,7 @@
       <c r="A210" s="2" t="n">
         <v>597826</v>
       </c>
-      <c r="B210" s="4" t="n">
+      <c r="B210" s="6" t="n">
         <v>42881.99998842592</v>
       </c>
       <c r="C210" s="2" t="inlineStr">
@@ -40089,7 +40090,7 @@
       <c r="A211" s="2" t="n">
         <v>597826</v>
       </c>
-      <c r="B211" s="4" t="n">
+      <c r="B211" s="6" t="n">
         <v>42991.38122685185</v>
       </c>
       <c r="C211" s="2" t="inlineStr">
@@ -40102,7 +40103,7 @@
       <c r="A212" s="2" t="n">
         <v>599134</v>
       </c>
-      <c r="B212" s="4" t="n">
+      <c r="B212" s="6" t="n">
         <v>40193</v>
       </c>
       <c r="C212" s="2" t="inlineStr">
@@ -40115,7 +40116,7 @@
       <c r="A213" s="2" t="n">
         <v>599134</v>
       </c>
-      <c r="B213" s="4" t="n">
+      <c r="B213" s="6" t="n">
         <v>45971.55646990741</v>
       </c>
       <c r="C213" s="2" t="inlineStr">
@@ -40128,7 +40129,7 @@
       <c r="A214" s="2" t="n">
         <v>842916</v>
       </c>
-      <c r="B214" s="4" t="n">
+      <c r="B214" s="6" t="n">
         <v>45226.44539351852</v>
       </c>
       <c r="C214" s="2" t="inlineStr">
@@ -40141,7 +40142,7 @@
       <c r="A215" s="2" t="n">
         <v>842916</v>
       </c>
-      <c r="B215" s="4" t="n">
+      <c r="B215" s="6" t="n">
         <v>45254.45302083333</v>
       </c>
       <c r="C215" s="2" t="inlineStr">
@@ -40154,7 +40155,7 @@
       <c r="A216" s="2" t="n">
         <v>842916</v>
       </c>
-      <c r="B216" s="4" t="n">
+      <c r="B216" s="6" t="n">
         <v>46161.61016203704</v>
       </c>
       <c r="C216" s="2" t="inlineStr">
@@ -40210,8 +40211,10 @@
       <c r="A2" s="2" t="n">
         <v>14770</v>
       </c>
-      <c r="B2" s="2" t="n">
-        <v>7.00710262018807e+18</v>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>07007102620188070018</t>
+        </is>
       </c>
       <c r="C2" s="2" t="inlineStr"/>
       <c r="D2" s="2" t="inlineStr"/>
@@ -40220,7 +40223,7 @@
       <c r="A3" s="2" t="n">
         <v>31043</v>
       </c>
-      <c r="B3" s="2" t="inlineStr"/>
+      <c r="B3" s="2" t="n"/>
       <c r="C3" s="2" t="inlineStr"/>
       <c r="D3" s="2" t="inlineStr"/>
     </row>
@@ -40228,7 +40231,7 @@
       <c r="A4" s="2" t="n">
         <v>54782</v>
       </c>
-      <c r="B4" s="2" t="inlineStr"/>
+      <c r="B4" s="2" t="n"/>
       <c r="C4" s="2" t="inlineStr"/>
       <c r="D4" s="2" t="inlineStr"/>
     </row>
@@ -40236,7 +40239,7 @@
       <c r="A5" s="2" t="n">
         <v>61182</v>
       </c>
-      <c r="B5" s="2" t="inlineStr"/>
+      <c r="B5" s="2" t="n"/>
       <c r="C5" s="2" t="inlineStr"/>
       <c r="D5" s="2" t="inlineStr"/>
     </row>
@@ -40244,8 +40247,10 @@
       <c r="A6" s="2" t="n">
         <v>62893</v>
       </c>
-      <c r="B6" s="2" t="n">
-        <v>7.10340432017807e+18</v>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>07103404320178070018</t>
+        </is>
       </c>
       <c r="C6" s="2" t="inlineStr"/>
       <c r="D6" s="2" t="inlineStr"/>
@@ -40254,8 +40259,10 @@
       <c r="A7" s="2" t="n">
         <v>62893</v>
       </c>
-      <c r="B7" s="2" t="n">
-        <v>7.50612462021807e+18</v>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>07506124620218070016</t>
+        </is>
       </c>
       <c r="C7" s="2" t="inlineStr"/>
       <c r="D7" s="2" t="inlineStr"/>
@@ -40264,8 +40271,10 @@
       <c r="A8" s="2" t="n">
         <v>62893</v>
       </c>
-      <c r="B8" s="2" t="n">
-        <v>20100110093278</v>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>20100110093278</t>
+        </is>
       </c>
       <c r="C8" s="2" t="inlineStr"/>
       <c r="D8" s="2" t="inlineStr"/>
@@ -40274,7 +40283,7 @@
       <c r="A9" s="2" t="n">
         <v>63548</v>
       </c>
-      <c r="B9" s="2" t="inlineStr"/>
+      <c r="B9" s="2" t="n"/>
       <c r="C9" s="2" t="inlineStr"/>
       <c r="D9" s="2" t="inlineStr"/>
     </row>
@@ -40282,8 +40291,10 @@
       <c r="A10" s="2" t="n">
         <v>64341</v>
       </c>
-      <c r="B10" s="2" t="n">
-        <v>20130110928657</v>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>20130110928657</t>
+        </is>
       </c>
       <c r="C10" s="2" t="inlineStr"/>
       <c r="D10" s="2" t="inlineStr"/>
@@ -40292,7 +40303,7 @@
       <c r="A11" s="2" t="n">
         <v>70919</v>
       </c>
-      <c r="B11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="n"/>
       <c r="C11" s="2" t="inlineStr"/>
       <c r="D11" s="2" t="inlineStr"/>
     </row>
@@ -40300,8 +40311,10 @@
       <c r="A12" s="2" t="n">
         <v>104370</v>
       </c>
-      <c r="B12" s="2" t="n">
-        <v>9853620125100000</v>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>00009853620125100004</t>
+        </is>
       </c>
       <c r="C12" s="2" t="inlineStr"/>
       <c r="D12" s="2" t="inlineStr"/>
@@ -40310,8 +40323,10 @@
       <c r="A13" s="2" t="n">
         <v>104370</v>
       </c>
-      <c r="B13" s="2" t="n">
-        <v>20120110850350</v>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>20120110850350</t>
+        </is>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
       <c r="D13" s="2" t="inlineStr">
@@ -40326,8 +40341,10 @@
       <c r="A14" s="2" t="n">
         <v>104370</v>
       </c>
-      <c r="B14" s="2" t="n">
-        <v>2.920037200351e+17</v>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>00292003720035100004</t>
+        </is>
       </c>
       <c r="C14" s="2" t="inlineStr"/>
       <c r="D14" s="2" t="inlineStr"/>
@@ -40336,8 +40353,10 @@
       <c r="A15" s="2" t="n">
         <v>104371</v>
       </c>
-      <c r="B15" s="2" t="n">
-        <v>2.920037200351e+17</v>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>00292003720035100004</t>
+        </is>
       </c>
       <c r="C15" s="2" t="inlineStr"/>
       <c r="D15" s="2" t="inlineStr"/>
@@ -40346,8 +40365,10 @@
       <c r="A16" s="2" t="n">
         <v>104371</v>
       </c>
-      <c r="B16" s="2" t="n">
-        <v>9853620125100000</v>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>00009853620125100004</t>
+        </is>
       </c>
       <c r="C16" s="2" t="inlineStr"/>
       <c r="D16" s="2" t="inlineStr"/>
@@ -40356,8 +40377,10 @@
       <c r="A17" s="2" t="n">
         <v>104371</v>
       </c>
-      <c r="B17" s="2" t="n">
-        <v>20120110850350</v>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>20120110850350</t>
+        </is>
       </c>
       <c r="C17" s="2" t="inlineStr"/>
       <c r="D17" s="2" t="inlineStr">
@@ -40372,8 +40395,10 @@
       <c r="A18" s="2" t="n">
         <v>104372</v>
       </c>
-      <c r="B18" s="2" t="n">
-        <v>20120110850350</v>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>20120110850350</t>
+        </is>
       </c>
       <c r="C18" s="2" t="inlineStr"/>
       <c r="D18" s="2" t="inlineStr">
@@ -40388,8 +40413,10 @@
       <c r="A19" s="2" t="n">
         <v>104372</v>
       </c>
-      <c r="B19" s="2" t="n">
-        <v>9853620125100000</v>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>00009853620125100004</t>
+        </is>
       </c>
       <c r="C19" s="2" t="inlineStr"/>
       <c r="D19" s="2" t="inlineStr"/>
@@ -40398,8 +40425,10 @@
       <c r="A20" s="2" t="n">
         <v>104372</v>
       </c>
-      <c r="B20" s="2" t="n">
-        <v>2.920037200351e+17</v>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>00292003720035100004</t>
+        </is>
       </c>
       <c r="C20" s="2" t="inlineStr"/>
       <c r="D20" s="2" t="inlineStr"/>
@@ -40408,8 +40437,10 @@
       <c r="A21" s="2" t="n">
         <v>109437</v>
       </c>
-      <c r="B21" s="2" t="n">
-        <v>7.09049282018807e+18</v>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>07090492820188070000</t>
+        </is>
       </c>
       <c r="C21" s="2" t="inlineStr"/>
       <c r="D21" s="2" t="inlineStr"/>
@@ -40418,8 +40449,10 @@
       <c r="A22" s="2" t="n">
         <v>109437</v>
       </c>
-      <c r="B22" s="2" t="n">
-        <v>20020001481816</v>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>20020001481816</t>
+        </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
@@ -40432,8 +40465,10 @@
       <c r="A23" s="2" t="n">
         <v>109437</v>
       </c>
-      <c r="B23" s="2" t="n">
-        <v>19990110485822</v>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>19990110485822</t>
+        </is>
       </c>
       <c r="C23" s="2" t="inlineStr"/>
       <c r="D23" s="2" t="inlineStr">
@@ -40460,8 +40495,10 @@
       <c r="A24" s="2" t="n">
         <v>109437</v>
       </c>
-      <c r="B24" s="2" t="n">
-        <v>7.33765172021807e+18</v>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>07337651720218070000</t>
+        </is>
       </c>
       <c r="C24" s="2" t="inlineStr"/>
       <c r="D24" s="2" t="inlineStr"/>
@@ -40470,8 +40507,10 @@
       <c r="A25" s="2" t="n">
         <v>109437</v>
       </c>
-      <c r="B25" s="2" t="n">
-        <v>7.05899772021807e+18</v>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>07058997720218070018</t>
+        </is>
       </c>
       <c r="C25" s="2" t="inlineStr"/>
       <c r="D25" s="2" t="inlineStr"/>
@@ -40480,8 +40519,10 @@
       <c r="A26" s="2" t="n">
         <v>109437</v>
       </c>
-      <c r="B26" s="2" t="n">
-        <v>20140020034910</v>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>20140020034910</t>
+        </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
@@ -40494,8 +40535,10 @@
       <c r="A27" s="2" t="n">
         <v>164319</v>
       </c>
-      <c r="B27" s="2" t="n">
-        <v>7.22833222021807e+18</v>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>07228332220218070015</t>
+        </is>
       </c>
       <c r="C27" s="2" t="inlineStr"/>
       <c r="D27" s="2" t="inlineStr"/>
@@ -40504,8 +40547,10 @@
       <c r="A28" s="2" t="n">
         <v>164320</v>
       </c>
-      <c r="B28" s="2" t="n">
-        <v>7.22833222021807e+18</v>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>07228332220218070015</t>
+        </is>
       </c>
       <c r="C28" s="2" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
@@ -40514,7 +40559,7 @@
       <c r="A29" s="2" t="n">
         <v>164325</v>
       </c>
-      <c r="B29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="n"/>
       <c r="C29" s="2" t="inlineStr"/>
       <c r="D29" s="2" t="inlineStr"/>
     </row>
@@ -40522,7 +40567,7 @@
       <c r="A30" s="2" t="n">
         <v>164326</v>
       </c>
-      <c r="B30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="n"/>
       <c r="C30" s="2" t="inlineStr"/>
       <c r="D30" s="2" t="inlineStr"/>
     </row>
@@ -40530,7 +40575,7 @@
       <c r="A31" s="2" t="n">
         <v>164327</v>
       </c>
-      <c r="B31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="n"/>
       <c r="C31" s="2" t="inlineStr"/>
       <c r="D31" s="2" t="inlineStr"/>
     </row>
@@ -40538,8 +40583,10 @@
       <c r="A32" s="2" t="n">
         <v>211948</v>
       </c>
-      <c r="B32" s="2" t="n">
-        <v>7.22464972026807e+18</v>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>07224649720268070000</t>
+        </is>
       </c>
       <c r="C32" s="2" t="inlineStr"/>
       <c r="D32" s="2" t="inlineStr"/>
@@ -40548,8 +40595,10 @@
       <c r="A33" s="2" t="n">
         <v>211948</v>
       </c>
-      <c r="B33" s="2" t="n">
-        <v>7.23984052020807e+18</v>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>07239840520208070000</t>
+        </is>
       </c>
       <c r="C33" s="2" t="inlineStr"/>
       <c r="D33" s="2" t="inlineStr"/>
@@ -40558,8 +40607,10 @@
       <c r="A34" s="2" t="n">
         <v>211948</v>
       </c>
-      <c r="B34" s="2" t="n">
-        <v>19980110018745</v>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>19980110018745</t>
+        </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
@@ -40572,8 +40623,10 @@
       <c r="A35" s="2" t="n">
         <v>211948</v>
       </c>
-      <c r="B35" s="2" t="n">
-        <v>20140111970194</v>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>20140111970194</t>
+        </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
@@ -40586,8 +40639,10 @@
       <c r="A36" s="2" t="n">
         <v>211948</v>
       </c>
-      <c r="B36" s="2" t="n">
-        <v>20130110603603</v>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>20130110603603</t>
+        </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
@@ -40600,8 +40655,10 @@
       <c r="A37" s="2" t="n">
         <v>211948</v>
       </c>
-      <c r="B37" s="2" t="n">
-        <v>20130110296220</v>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>20130110296220</t>
+        </is>
       </c>
       <c r="C37" s="2" t="inlineStr"/>
       <c r="D37" s="2" t="inlineStr"/>
@@ -40610,8 +40667,10 @@
       <c r="A38" s="2" t="n">
         <v>211948</v>
       </c>
-      <c r="B38" s="2" t="n">
-        <v>7.50500232024807e+18</v>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>07505002320248070000</t>
+        </is>
       </c>
       <c r="C38" s="2" t="inlineStr"/>
       <c r="D38" s="2" t="inlineStr"/>
@@ -40620,8 +40679,10 @@
       <c r="A39" s="2" t="n">
         <v>211948</v>
       </c>
-      <c r="B39" s="2" t="n">
-        <v>7.00636982020807e+18</v>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>07006369820208070018</t>
+        </is>
       </c>
       <c r="C39" s="2" t="inlineStr"/>
       <c r="D39" s="2" t="inlineStr"/>
@@ -40630,8 +40691,10 @@
       <c r="A40" s="2" t="n">
         <v>211948</v>
       </c>
-      <c r="B40" s="2" t="n">
-        <v>7.03334772020807e+18</v>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>07033347720208070018</t>
+        </is>
       </c>
       <c r="C40" s="2" t="inlineStr"/>
       <c r="D40" s="2" t="inlineStr"/>
@@ -40640,8 +40703,10 @@
       <c r="A41" s="2" t="n">
         <v>211948</v>
       </c>
-      <c r="B41" s="2" t="n">
-        <v>7.18170162024807e+18</v>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>07181701620248070018</t>
+        </is>
       </c>
       <c r="C41" s="2" t="inlineStr"/>
       <c r="D41" s="2" t="inlineStr"/>
@@ -40650,8 +40715,10 @@
       <c r="A42" s="2" t="n">
         <v>211948</v>
       </c>
-      <c r="B42" s="2" t="n">
-        <v>1.095402020251e+18</v>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>01095402020251000000</t>
+        </is>
       </c>
       <c r="C42" s="2" t="inlineStr"/>
       <c r="D42" s="2" t="inlineStr"/>
@@ -40660,8 +40727,10 @@
       <c r="A43" s="2" t="n">
         <v>212548</v>
       </c>
-      <c r="B43" s="2" t="n">
-        <v>7.44062982022807e+18</v>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>07440629820228070016</t>
+        </is>
       </c>
       <c r="C43" s="2" t="inlineStr"/>
       <c r="D43" s="2" t="inlineStr">
@@ -40675,8 +40744,10 @@
       <c r="A44" s="2" t="n">
         <v>212548</v>
       </c>
-      <c r="B44" s="2" t="n">
-        <v>7.50611612021807e+18</v>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>07506116120218070016</t>
+        </is>
       </c>
       <c r="C44" s="2" t="inlineStr"/>
       <c r="D44" s="2" t="inlineStr">
@@ -40690,8 +40761,10 @@
       <c r="A45" s="2" t="n">
         <v>492096</v>
       </c>
-      <c r="B45" s="2" t="n">
-        <v>7.32728092018807e+18</v>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>07327280920188070016</t>
+        </is>
       </c>
       <c r="C45" s="2" t="inlineStr"/>
       <c r="D45" s="2" t="inlineStr"/>
@@ -40700,8 +40773,10 @@
       <c r="A46" s="2" t="n">
         <v>492096</v>
       </c>
-      <c r="B46" s="2" t="n">
-        <v>7.02915572020807e+18</v>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>07029155720208070018</t>
+        </is>
       </c>
       <c r="C46" s="2" t="inlineStr"/>
       <c r="D46" s="2" t="inlineStr"/>
@@ -40710,8 +40785,10 @@
       <c r="A47" s="2" t="n">
         <v>492096</v>
       </c>
-      <c r="B47" s="2" t="n">
-        <v>7.08577362019807e+18</v>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>07085773620198070018</t>
+        </is>
       </c>
       <c r="C47" s="2" t="inlineStr"/>
       <c r="D47" s="2" t="inlineStr"/>
@@ -40720,8 +40797,10 @@
       <c r="A48" s="2" t="n">
         <v>492096</v>
       </c>
-      <c r="B48" s="2" t="n">
-        <v>20160111018656</v>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>20160111018656</t>
+        </is>
       </c>
       <c r="C48" s="2" t="inlineStr"/>
       <c r="D48" s="2" t="inlineStr"/>
@@ -40730,7 +40809,7 @@
       <c r="A49" s="2" t="n">
         <v>522083</v>
       </c>
-      <c r="B49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="n"/>
       <c r="C49" s="2" t="inlineStr"/>
       <c r="D49" s="2" t="inlineStr"/>
     </row>
@@ -40738,8 +40817,10 @@
       <c r="A50" s="2" t="n">
         <v>523843</v>
       </c>
-      <c r="B50" s="2" t="n">
-        <v>7.38820722023807e+18</v>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>07388207220238070001</t>
+        </is>
       </c>
       <c r="C50" s="2" t="inlineStr"/>
       <c r="D50" s="2" t="inlineStr"/>
@@ -40748,8 +40829,10 @@
       <c r="A51" s="2" t="n">
         <v>523844</v>
       </c>
-      <c r="B51" s="2" t="n">
-        <v>7.38820722023807e+18</v>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>07388207220238070001</t>
+        </is>
       </c>
       <c r="C51" s="2" t="inlineStr"/>
       <c r="D51" s="2" t="inlineStr"/>
@@ -40758,8 +40841,10 @@
       <c r="A52" s="2" t="n">
         <v>523845</v>
       </c>
-      <c r="B52" s="2" t="n">
-        <v>7.38820722023807e+18</v>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>07388207220238070001</t>
+        </is>
       </c>
       <c r="C52" s="2" t="inlineStr"/>
       <c r="D52" s="2" t="inlineStr"/>
@@ -40768,8 +40853,10 @@
       <c r="A53" s="2" t="n">
         <v>523846</v>
       </c>
-      <c r="B53" s="2" t="n">
-        <v>7.38820722023807e+18</v>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>07388207220238070001</t>
+        </is>
       </c>
       <c r="C53" s="2" t="inlineStr"/>
       <c r="D53" s="2" t="inlineStr"/>
@@ -40778,7 +40865,7 @@
       <c r="A54" s="2" t="n">
         <v>523849</v>
       </c>
-      <c r="B54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="n"/>
       <c r="C54" s="2" t="inlineStr"/>
       <c r="D54" s="2" t="inlineStr"/>
     </row>
@@ -40786,7 +40873,7 @@
       <c r="A55" s="2" t="n">
         <v>523854</v>
       </c>
-      <c r="B55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="n"/>
       <c r="C55" s="2" t="inlineStr"/>
       <c r="D55" s="2" t="inlineStr"/>
     </row>
@@ -40794,7 +40881,7 @@
       <c r="A56" s="2" t="n">
         <v>523856</v>
       </c>
-      <c r="B56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="n"/>
       <c r="C56" s="2" t="inlineStr"/>
       <c r="D56" s="2" t="inlineStr"/>
     </row>
@@ -40802,7 +40889,7 @@
       <c r="A57" s="2" t="n">
         <v>523860</v>
       </c>
-      <c r="B57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="n"/>
       <c r="C57" s="2" t="inlineStr"/>
       <c r="D57" s="2" t="inlineStr"/>
     </row>
@@ -40810,7 +40897,7 @@
       <c r="A58" s="2" t="n">
         <v>523866</v>
       </c>
-      <c r="B58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="n"/>
       <c r="C58" s="2" t="inlineStr"/>
       <c r="D58" s="2" t="inlineStr"/>
     </row>
@@ -40818,7 +40905,7 @@
       <c r="A59" s="2" t="n">
         <v>593604</v>
       </c>
-      <c r="B59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="n"/>
       <c r="C59" s="2" t="inlineStr"/>
       <c r="D59" s="2" t="inlineStr"/>
     </row>
@@ -40826,7 +40913,7 @@
       <c r="A60" s="2" t="n">
         <v>593607</v>
       </c>
-      <c r="B60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="n"/>
       <c r="C60" s="2" t="inlineStr"/>
       <c r="D60" s="2" t="inlineStr"/>
     </row>
@@ -40834,8 +40921,10 @@
       <c r="A61" s="2" t="n">
         <v>593716</v>
       </c>
-      <c r="B61" s="2" t="n">
-        <v>7.05104422019807e+18</v>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>07051044220198070018</t>
+        </is>
       </c>
       <c r="C61" s="2" t="inlineStr"/>
       <c r="D61" s="2" t="inlineStr"/>
@@ -40844,8 +40933,10 @@
       <c r="A62" s="2" t="n">
         <v>593725</v>
       </c>
-      <c r="B62" s="2" t="n">
-        <v>7.08525112017807e+18</v>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>07085251120178070018</t>
+        </is>
       </c>
       <c r="C62" s="2" t="inlineStr"/>
       <c r="D62" s="2" t="inlineStr"/>
@@ -40854,8 +40945,10 @@
       <c r="A63" s="2" t="n">
         <v>593725</v>
       </c>
-      <c r="B63" s="2" t="n">
-        <v>7.02224042024807e+18</v>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>07022240420248070018</t>
+        </is>
       </c>
       <c r="C63" s="2" t="inlineStr"/>
       <c r="D63" s="2" t="inlineStr"/>
@@ -40864,8 +40957,10 @@
       <c r="A64" s="2" t="n">
         <v>593725</v>
       </c>
-      <c r="B64" s="2" t="n">
-        <v>7.15870382024807e+18</v>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>07158703820248070000</t>
+        </is>
       </c>
       <c r="C64" s="2" t="inlineStr"/>
       <c r="D64" s="2" t="inlineStr"/>
@@ -40874,8 +40969,10 @@
       <c r="A65" s="2" t="n">
         <v>593725</v>
       </c>
-      <c r="B65" s="2" t="n">
-        <v>20160110396955</v>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>20160110396955</t>
+        </is>
       </c>
       <c r="C65" s="2" t="inlineStr"/>
       <c r="D65" s="2" t="inlineStr"/>
@@ -40884,8 +40981,10 @@
       <c r="A66" s="2" t="n">
         <v>593880</v>
       </c>
-      <c r="B66" s="2" t="n">
-        <v>7.00645602020807e+18</v>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>07006456020208070018</t>
+        </is>
       </c>
       <c r="C66" s="2" t="inlineStr"/>
       <c r="D66" s="2" t="inlineStr"/>
@@ -40894,8 +40993,10 @@
       <c r="A67" s="2" t="n">
         <v>593880</v>
       </c>
-      <c r="B67" s="2" t="n">
-        <v>20150111330483</v>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>20150111330483</t>
+        </is>
       </c>
       <c r="C67" s="2" t="inlineStr"/>
       <c r="D67" s="2" t="inlineStr"/>
@@ -40904,7 +41005,7 @@
       <c r="A68" s="2" t="n">
         <v>597826</v>
       </c>
-      <c r="B68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="n"/>
       <c r="C68" s="2" t="inlineStr"/>
       <c r="D68" s="2" t="inlineStr"/>
     </row>
@@ -40912,8 +41013,10 @@
       <c r="A69" s="2" t="n">
         <v>599134</v>
       </c>
-      <c r="B69" s="2" t="n">
-        <v>20140110765974</v>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>20140110765974</t>
+        </is>
       </c>
       <c r="C69" s="2" t="inlineStr"/>
       <c r="D69" s="2" t="inlineStr"/>
@@ -40922,8 +41025,10 @@
       <c r="A70" s="2" t="n">
         <v>599134</v>
       </c>
-      <c r="B70" s="2" t="n">
-        <v>7.05935222021807e+18</v>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>07059352220218070018</t>
+        </is>
       </c>
       <c r="C70" s="2" t="inlineStr"/>
       <c r="D70" s="2" t="inlineStr"/>
@@ -40932,8 +41037,10 @@
       <c r="A71" s="2" t="n">
         <v>599134</v>
       </c>
-      <c r="B71" s="2" t="n">
-        <v>20170110329988</v>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>20170110329988</t>
+        </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
@@ -40946,7 +41053,7 @@
       <c r="A72" s="2" t="n">
         <v>806921</v>
       </c>
-      <c r="B72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="n"/>
       <c r="C72" s="2" t="inlineStr"/>
       <c r="D72" s="2" t="inlineStr"/>
     </row>
@@ -40954,7 +41061,7 @@
       <c r="A73" s="2" t="n">
         <v>806923</v>
       </c>
-      <c r="B73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="n"/>
       <c r="C73" s="2" t="inlineStr"/>
       <c r="D73" s="2" t="inlineStr"/>
     </row>
@@ -40962,7 +41069,7 @@
       <c r="A74" s="2" t="n">
         <v>806927</v>
       </c>
-      <c r="B74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="n"/>
       <c r="C74" s="2" t="inlineStr"/>
       <c r="D74" s="2" t="inlineStr"/>
     </row>
@@ -40970,7 +41077,7 @@
       <c r="A75" s="2" t="n">
         <v>806928</v>
       </c>
-      <c r="B75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="n"/>
       <c r="C75" s="2" t="inlineStr"/>
       <c r="D75" s="2" t="inlineStr"/>
     </row>
@@ -40978,7 +41085,7 @@
       <c r="A76" s="2" t="n">
         <v>806929</v>
       </c>
-      <c r="B76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="n"/>
       <c r="C76" s="2" t="inlineStr"/>
       <c r="D76" s="2" t="inlineStr"/>
     </row>
@@ -40986,7 +41093,7 @@
       <c r="A77" s="2" t="n">
         <v>806930</v>
       </c>
-      <c r="B77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="n"/>
       <c r="C77" s="2" t="inlineStr"/>
       <c r="D77" s="2" t="inlineStr"/>
     </row>
@@ -40994,7 +41101,7 @@
       <c r="A78" s="2" t="n">
         <v>806931</v>
       </c>
-      <c r="B78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="n"/>
       <c r="C78" s="2" t="inlineStr"/>
       <c r="D78" s="2" t="inlineStr"/>
     </row>
@@ -41002,7 +41109,7 @@
       <c r="A79" s="2" t="n">
         <v>806932</v>
       </c>
-      <c r="B79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="n"/>
       <c r="C79" s="2" t="inlineStr"/>
       <c r="D79" s="2" t="inlineStr"/>
     </row>
@@ -41010,7 +41117,7 @@
       <c r="A80" s="2" t="n">
         <v>806933</v>
       </c>
-      <c r="B80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="n"/>
       <c r="C80" s="2" t="inlineStr"/>
       <c r="D80" s="2" t="inlineStr"/>
     </row>
@@ -41018,7 +41125,7 @@
       <c r="A81" s="2" t="n">
         <v>806934</v>
       </c>
-      <c r="B81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="n"/>
       <c r="C81" s="2" t="inlineStr"/>
       <c r="D81" s="2" t="inlineStr"/>
     </row>
@@ -41026,7 +41133,7 @@
       <c r="A82" s="2" t="n">
         <v>806935</v>
       </c>
-      <c r="B82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="n"/>
       <c r="C82" s="2" t="inlineStr"/>
       <c r="D82" s="2" t="inlineStr"/>
     </row>
@@ -41034,7 +41141,7 @@
       <c r="A83" s="2" t="n">
         <v>829054</v>
       </c>
-      <c r="B83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="n"/>
       <c r="C83" s="2" t="inlineStr"/>
       <c r="D83" s="2" t="inlineStr"/>
     </row>
@@ -41042,7 +41149,7 @@
       <c r="A84" s="2" t="n">
         <v>830271</v>
       </c>
-      <c r="B84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="n"/>
       <c r="C84" s="2" t="inlineStr"/>
       <c r="D84" s="2" t="inlineStr"/>
     </row>
@@ -41050,7 +41157,7 @@
       <c r="A85" s="2" t="n">
         <v>840622</v>
       </c>
-      <c r="B85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="n"/>
       <c r="C85" s="2" t="inlineStr"/>
       <c r="D85" s="2" t="inlineStr"/>
     </row>
@@ -41058,7 +41165,7 @@
       <c r="A86" s="2" t="n">
         <v>840623</v>
       </c>
-      <c r="B86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="n"/>
       <c r="C86" s="2" t="inlineStr"/>
       <c r="D86" s="2" t="inlineStr"/>
     </row>
@@ -41066,7 +41173,7 @@
       <c r="A87" s="2" t="n">
         <v>840625</v>
       </c>
-      <c r="B87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="n"/>
       <c r="C87" s="2" t="inlineStr"/>
       <c r="D87" s="2" t="inlineStr"/>
     </row>
@@ -41074,7 +41181,7 @@
       <c r="A88" s="2" t="n">
         <v>840627</v>
       </c>
-      <c r="B88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="n"/>
       <c r="C88" s="2" t="inlineStr"/>
       <c r="D88" s="2" t="inlineStr"/>
     </row>
@@ -41082,7 +41189,7 @@
       <c r="A89" s="2" t="n">
         <v>840628</v>
       </c>
-      <c r="B89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="n"/>
       <c r="C89" s="2" t="inlineStr"/>
       <c r="D89" s="2" t="inlineStr"/>
     </row>
@@ -41090,7 +41197,7 @@
       <c r="A90" s="2" t="n">
         <v>840629</v>
       </c>
-      <c r="B90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="n"/>
       <c r="C90" s="2" t="inlineStr"/>
       <c r="D90" s="2" t="inlineStr"/>
     </row>
@@ -41098,7 +41205,7 @@
       <c r="A91" s="2" t="n">
         <v>840630</v>
       </c>
-      <c r="B91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="n"/>
       <c r="C91" s="2" t="inlineStr"/>
       <c r="D91" s="2" t="inlineStr"/>
     </row>
@@ -41106,7 +41213,7 @@
       <c r="A92" s="2" t="n">
         <v>840631</v>
       </c>
-      <c r="B92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="n"/>
       <c r="C92" s="2" t="inlineStr"/>
       <c r="D92" s="2" t="inlineStr"/>
     </row>
@@ -41114,7 +41221,7 @@
       <c r="A93" s="2" t="n">
         <v>840633</v>
       </c>
-      <c r="B93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="n"/>
       <c r="C93" s="2" t="inlineStr"/>
       <c r="D93" s="2" t="inlineStr"/>
     </row>
@@ -41122,7 +41229,7 @@
       <c r="A94" s="2" t="n">
         <v>840634</v>
       </c>
-      <c r="B94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="n"/>
       <c r="C94" s="2" t="inlineStr"/>
       <c r="D94" s="2" t="inlineStr"/>
     </row>
@@ -41130,7 +41237,7 @@
       <c r="A95" s="2" t="n">
         <v>840637</v>
       </c>
-      <c r="B95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="n"/>
       <c r="C95" s="2" t="inlineStr"/>
       <c r="D95" s="2" t="inlineStr"/>
     </row>
@@ -41138,7 +41245,7 @@
       <c r="A96" s="2" t="n">
         <v>840638</v>
       </c>
-      <c r="B96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="n"/>
       <c r="C96" s="2" t="inlineStr"/>
       <c r="D96" s="2" t="inlineStr"/>
     </row>
@@ -41146,7 +41253,7 @@
       <c r="A97" s="2" t="n">
         <v>840639</v>
       </c>
-      <c r="B97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="n"/>
       <c r="C97" s="2" t="inlineStr"/>
       <c r="D97" s="2" t="inlineStr"/>
     </row>
@@ -41154,7 +41261,7 @@
       <c r="A98" s="2" t="n">
         <v>840640</v>
       </c>
-      <c r="B98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="n"/>
       <c r="C98" s="2" t="inlineStr"/>
       <c r="D98" s="2" t="inlineStr"/>
     </row>
@@ -41162,7 +41269,7 @@
       <c r="A99" s="2" t="n">
         <v>840641</v>
       </c>
-      <c r="B99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="n"/>
       <c r="C99" s="2" t="inlineStr"/>
       <c r="D99" s="2" t="inlineStr"/>
     </row>
@@ -41170,7 +41277,7 @@
       <c r="A100" s="2" t="n">
         <v>840772</v>
       </c>
-      <c r="B100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="n"/>
       <c r="C100" s="2" t="inlineStr"/>
       <c r="D100" s="2" t="inlineStr"/>
     </row>
@@ -41178,7 +41285,7 @@
       <c r="A101" s="2" t="n">
         <v>840773</v>
       </c>
-      <c r="B101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="n"/>
       <c r="C101" s="2" t="inlineStr"/>
       <c r="D101" s="2" t="inlineStr"/>
     </row>
@@ -41186,7 +41293,7 @@
       <c r="A102" s="2" t="n">
         <v>841600</v>
       </c>
-      <c r="B102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="n"/>
       <c r="C102" s="2" t="inlineStr"/>
       <c r="D102" s="2" t="inlineStr"/>
     </row>
@@ -41194,7 +41301,7 @@
       <c r="A103" s="2" t="n">
         <v>841601</v>
       </c>
-      <c r="B103" s="2" t="inlineStr"/>
+      <c r="B103" s="2" t="n"/>
       <c r="C103" s="2" t="inlineStr"/>
       <c r="D103" s="2" t="inlineStr"/>
     </row>
@@ -41202,7 +41309,7 @@
       <c r="A104" s="2" t="n">
         <v>841602</v>
       </c>
-      <c r="B104" s="2" t="inlineStr"/>
+      <c r="B104" s="2" t="n"/>
       <c r="C104" s="2" t="inlineStr"/>
       <c r="D104" s="2" t="inlineStr"/>
     </row>
@@ -41210,7 +41317,7 @@
       <c r="A105" s="2" t="n">
         <v>841603</v>
       </c>
-      <c r="B105" s="2" t="inlineStr"/>
+      <c r="B105" s="2" t="n"/>
       <c r="C105" s="2" t="inlineStr"/>
       <c r="D105" s="2" t="inlineStr"/>
     </row>
@@ -41218,7 +41325,7 @@
       <c r="A106" s="2" t="n">
         <v>841604</v>
       </c>
-      <c r="B106" s="2" t="inlineStr"/>
+      <c r="B106" s="2" t="n"/>
       <c r="C106" s="2" t="inlineStr"/>
       <c r="D106" s="2" t="inlineStr"/>
     </row>
@@ -41226,7 +41333,7 @@
       <c r="A107" s="2" t="n">
         <v>841605</v>
       </c>
-      <c r="B107" s="2" t="inlineStr"/>
+      <c r="B107" s="2" t="n"/>
       <c r="C107" s="2" t="inlineStr"/>
       <c r="D107" s="2" t="inlineStr"/>
     </row>
@@ -41234,7 +41341,7 @@
       <c r="A108" s="2" t="n">
         <v>841606</v>
       </c>
-      <c r="B108" s="2" t="inlineStr"/>
+      <c r="B108" s="2" t="n"/>
       <c r="C108" s="2" t="inlineStr"/>
       <c r="D108" s="2" t="inlineStr"/>
     </row>
@@ -41242,7 +41349,7 @@
       <c r="A109" s="2" t="n">
         <v>841609</v>
       </c>
-      <c r="B109" s="2" t="inlineStr"/>
+      <c r="B109" s="2" t="n"/>
       <c r="C109" s="2" t="inlineStr"/>
       <c r="D109" s="2" t="inlineStr"/>
     </row>
@@ -41250,7 +41357,7 @@
       <c r="A110" s="2" t="n">
         <v>841610</v>
       </c>
-      <c r="B110" s="2" t="inlineStr"/>
+      <c r="B110" s="2" t="n"/>
       <c r="C110" s="2" t="inlineStr"/>
       <c r="D110" s="2" t="inlineStr"/>
     </row>
@@ -41258,7 +41365,7 @@
       <c r="A111" s="2" t="n">
         <v>841611</v>
       </c>
-      <c r="B111" s="2" t="inlineStr"/>
+      <c r="B111" s="2" t="n"/>
       <c r="C111" s="2" t="inlineStr"/>
       <c r="D111" s="2" t="inlineStr"/>
     </row>
@@ -41266,7 +41373,7 @@
       <c r="A112" s="2" t="n">
         <v>841612</v>
       </c>
-      <c r="B112" s="2" t="inlineStr"/>
+      <c r="B112" s="2" t="n"/>
       <c r="C112" s="2" t="inlineStr"/>
       <c r="D112" s="2" t="inlineStr"/>
     </row>
@@ -41274,7 +41381,7 @@
       <c r="A113" s="2" t="n">
         <v>841613</v>
       </c>
-      <c r="B113" s="2" t="inlineStr"/>
+      <c r="B113" s="2" t="n"/>
       <c r="C113" s="2" t="inlineStr"/>
       <c r="D113" s="2" t="inlineStr"/>
     </row>
@@ -41282,7 +41389,7 @@
       <c r="A114" s="2" t="n">
         <v>841615</v>
       </c>
-      <c r="B114" s="2" t="inlineStr"/>
+      <c r="B114" s="2" t="n"/>
       <c r="C114" s="2" t="inlineStr"/>
       <c r="D114" s="2" t="inlineStr"/>
     </row>
@@ -41290,7 +41397,7 @@
       <c r="A115" s="2" t="n">
         <v>841617</v>
       </c>
-      <c r="B115" s="2" t="inlineStr"/>
+      <c r="B115" s="2" t="n"/>
       <c r="C115" s="2" t="inlineStr"/>
       <c r="D115" s="2" t="inlineStr"/>
     </row>
@@ -41298,7 +41405,7 @@
       <c r="A116" s="2" t="n">
         <v>841619</v>
       </c>
-      <c r="B116" s="2" t="inlineStr"/>
+      <c r="B116" s="2" t="n"/>
       <c r="C116" s="2" t="inlineStr"/>
       <c r="D116" s="2" t="inlineStr"/>
     </row>
@@ -41306,7 +41413,7 @@
       <c r="A117" s="2" t="n">
         <v>841621</v>
       </c>
-      <c r="B117" s="2" t="inlineStr"/>
+      <c r="B117" s="2" t="n"/>
       <c r="C117" s="2" t="inlineStr"/>
       <c r="D117" s="2" t="inlineStr"/>
     </row>
@@ -41314,7 +41421,7 @@
       <c r="A118" s="2" t="n">
         <v>841623</v>
       </c>
-      <c r="B118" s="2" t="inlineStr"/>
+      <c r="B118" s="2" t="n"/>
       <c r="C118" s="2" t="inlineStr"/>
       <c r="D118" s="2" t="inlineStr"/>
     </row>
@@ -41322,7 +41429,7 @@
       <c r="A119" s="2" t="n">
         <v>841625</v>
       </c>
-      <c r="B119" s="2" t="inlineStr"/>
+      <c r="B119" s="2" t="n"/>
       <c r="C119" s="2" t="inlineStr"/>
       <c r="D119" s="2" t="inlineStr"/>
     </row>
@@ -41330,7 +41437,7 @@
       <c r="A120" s="2" t="n">
         <v>841627</v>
       </c>
-      <c r="B120" s="2" t="inlineStr"/>
+      <c r="B120" s="2" t="n"/>
       <c r="C120" s="2" t="inlineStr"/>
       <c r="D120" s="2" t="inlineStr"/>
     </row>
@@ -41338,7 +41445,7 @@
       <c r="A121" s="2" t="n">
         <v>841629</v>
       </c>
-      <c r="B121" s="2" t="inlineStr"/>
+      <c r="B121" s="2" t="n"/>
       <c r="C121" s="2" t="inlineStr"/>
       <c r="D121" s="2" t="inlineStr"/>
     </row>
@@ -41346,7 +41453,7 @@
       <c r="A122" s="2" t="n">
         <v>841640</v>
       </c>
-      <c r="B122" s="2" t="inlineStr"/>
+      <c r="B122" s="2" t="n"/>
       <c r="C122" s="2" t="inlineStr"/>
       <c r="D122" s="2" t="inlineStr"/>
     </row>
@@ -41354,7 +41461,7 @@
       <c r="A123" s="2" t="n">
         <v>841642</v>
       </c>
-      <c r="B123" s="2" t="inlineStr"/>
+      <c r="B123" s="2" t="n"/>
       <c r="C123" s="2" t="inlineStr"/>
       <c r="D123" s="2" t="inlineStr"/>
     </row>
@@ -41362,7 +41469,7 @@
       <c r="A124" s="2" t="n">
         <v>841644</v>
       </c>
-      <c r="B124" s="2" t="inlineStr"/>
+      <c r="B124" s="2" t="n"/>
       <c r="C124" s="2" t="inlineStr"/>
       <c r="D124" s="2" t="inlineStr"/>
     </row>
@@ -41370,7 +41477,7 @@
       <c r="A125" s="2" t="n">
         <v>841646</v>
       </c>
-      <c r="B125" s="2" t="inlineStr"/>
+      <c r="B125" s="2" t="n"/>
       <c r="C125" s="2" t="inlineStr"/>
       <c r="D125" s="2" t="inlineStr"/>
     </row>
@@ -41378,7 +41485,7 @@
       <c r="A126" s="2" t="n">
         <v>841648</v>
       </c>
-      <c r="B126" s="2" t="inlineStr"/>
+      <c r="B126" s="2" t="n"/>
       <c r="C126" s="2" t="inlineStr"/>
       <c r="D126" s="2" t="inlineStr"/>
     </row>
@@ -41386,7 +41493,7 @@
       <c r="A127" s="2" t="n">
         <v>841650</v>
       </c>
-      <c r="B127" s="2" t="inlineStr"/>
+      <c r="B127" s="2" t="n"/>
       <c r="C127" s="2" t="inlineStr"/>
       <c r="D127" s="2" t="inlineStr"/>
     </row>
@@ -41394,7 +41501,7 @@
       <c r="A128" s="2" t="n">
         <v>841651</v>
       </c>
-      <c r="B128" s="2" t="inlineStr"/>
+      <c r="B128" s="2" t="n"/>
       <c r="C128" s="2" t="inlineStr"/>
       <c r="D128" s="2" t="inlineStr"/>
     </row>
@@ -41402,7 +41509,7 @@
       <c r="A129" s="2" t="n">
         <v>841654</v>
       </c>
-      <c r="B129" s="2" t="inlineStr"/>
+      <c r="B129" s="2" t="n"/>
       <c r="C129" s="2" t="inlineStr"/>
       <c r="D129" s="2" t="inlineStr"/>
     </row>
@@ -41410,7 +41517,7 @@
       <c r="A130" s="2" t="n">
         <v>841656</v>
       </c>
-      <c r="B130" s="2" t="inlineStr"/>
+      <c r="B130" s="2" t="n"/>
       <c r="C130" s="2" t="inlineStr"/>
       <c r="D130" s="2" t="inlineStr"/>
     </row>
@@ -41418,7 +41525,7 @@
       <c r="A131" s="2" t="n">
         <v>841658</v>
       </c>
-      <c r="B131" s="2" t="inlineStr"/>
+      <c r="B131" s="2" t="n"/>
       <c r="C131" s="2" t="inlineStr"/>
       <c r="D131" s="2" t="inlineStr"/>
     </row>
@@ -41426,7 +41533,7 @@
       <c r="A132" s="2" t="n">
         <v>841660</v>
       </c>
-      <c r="B132" s="2" t="inlineStr"/>
+      <c r="B132" s="2" t="n"/>
       <c r="C132" s="2" t="inlineStr"/>
       <c r="D132" s="2" t="inlineStr"/>
     </row>
@@ -41434,7 +41541,7 @@
       <c r="A133" s="2" t="n">
         <v>841662</v>
       </c>
-      <c r="B133" s="2" t="inlineStr"/>
+      <c r="B133" s="2" t="n"/>
       <c r="C133" s="2" t="inlineStr"/>
       <c r="D133" s="2" t="inlineStr"/>
     </row>
@@ -41442,7 +41549,7 @@
       <c r="A134" s="2" t="n">
         <v>841664</v>
       </c>
-      <c r="B134" s="2" t="inlineStr"/>
+      <c r="B134" s="2" t="n"/>
       <c r="C134" s="2" t="inlineStr"/>
       <c r="D134" s="2" t="inlineStr"/>
     </row>
@@ -41450,7 +41557,7 @@
       <c r="A135" s="2" t="n">
         <v>841665</v>
       </c>
-      <c r="B135" s="2" t="inlineStr"/>
+      <c r="B135" s="2" t="n"/>
       <c r="C135" s="2" t="inlineStr"/>
       <c r="D135" s="2" t="inlineStr"/>
     </row>
@@ -41458,7 +41565,7 @@
       <c r="A136" s="2" t="n">
         <v>841672</v>
       </c>
-      <c r="B136" s="2" t="inlineStr"/>
+      <c r="B136" s="2" t="n"/>
       <c r="C136" s="2" t="inlineStr"/>
       <c r="D136" s="2" t="inlineStr"/>
     </row>
@@ -41466,7 +41573,7 @@
       <c r="A137" s="2" t="n">
         <v>841674</v>
       </c>
-      <c r="B137" s="2" t="inlineStr"/>
+      <c r="B137" s="2" t="n"/>
       <c r="C137" s="2" t="inlineStr"/>
       <c r="D137" s="2" t="inlineStr"/>
     </row>
@@ -41474,7 +41581,7 @@
       <c r="A138" s="2" t="n">
         <v>841675</v>
       </c>
-      <c r="B138" s="2" t="inlineStr"/>
+      <c r="B138" s="2" t="n"/>
       <c r="C138" s="2" t="inlineStr"/>
       <c r="D138" s="2" t="inlineStr"/>
     </row>
@@ -41482,7 +41589,7 @@
       <c r="A139" s="2" t="n">
         <v>841682</v>
       </c>
-      <c r="B139" s="2" t="inlineStr"/>
+      <c r="B139" s="2" t="n"/>
       <c r="C139" s="2" t="inlineStr"/>
       <c r="D139" s="2" t="inlineStr"/>
     </row>
@@ -41490,7 +41597,7 @@
       <c r="A140" s="2" t="n">
         <v>841686</v>
       </c>
-      <c r="B140" s="2" t="inlineStr"/>
+      <c r="B140" s="2" t="n"/>
       <c r="C140" s="2" t="inlineStr"/>
       <c r="D140" s="2" t="inlineStr"/>
     </row>
@@ -41498,7 +41605,7 @@
       <c r="A141" s="2" t="n">
         <v>842916</v>
       </c>
-      <c r="B141" s="2" t="inlineStr"/>
+      <c r="B141" s="2" t="n"/>
       <c r="C141" s="2" t="inlineStr"/>
       <c r="D141" s="2" t="inlineStr"/>
     </row>
@@ -41506,8 +41613,10 @@
       <c r="A142" s="2" t="n">
         <v>855441</v>
       </c>
-      <c r="B142" s="2" t="n">
-        <v>7.14110632025807e+18</v>
+      <c r="B142" s="7" t="inlineStr">
+        <is>
+          <t>07141106320258070018</t>
+        </is>
       </c>
       <c r="C142" s="2" t="inlineStr"/>
       <c r="D142" s="2" t="inlineStr"/>
@@ -41516,8 +41625,10 @@
       <c r="A143" s="2" t="n">
         <v>855441</v>
       </c>
-      <c r="B143" s="2" t="n">
-        <v>7.47126622025807e+18</v>
+      <c r="B143" s="7" t="inlineStr">
+        <is>
+          <t>07471266220258070000</t>
+        </is>
       </c>
       <c r="C143" s="2" t="inlineStr"/>
       <c r="D143" s="2" t="inlineStr"/>
@@ -41578,7 +41689,7 @@
       <c r="B2" s="2" t="n">
         <v>785</v>
       </c>
-      <c r="C2" s="4" t="n">
+      <c r="C2" s="6" t="n">
         <v>29987</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -41599,7 +41710,7 @@
       <c r="B3" s="2" t="n">
         <v>95189</v>
       </c>
-      <c r="C3" s="4" t="n">
+      <c r="C3" s="6" t="n">
         <v>40526</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -41620,7 +41731,7 @@
       <c r="B4" s="2" t="n">
         <v>5389</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C4" s="6" t="n">
         <v>29478</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -41641,7 +41752,7 @@
       <c r="B5" s="2" t="n">
         <v>27334</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="6" t="n">
         <v>34043</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -41662,7 +41773,7 @@
       <c r="B6" s="2" t="n">
         <v>33723</v>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C6" s="6" t="n">
         <v>33368</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -41683,7 +41794,7 @@
       <c r="B7" s="2" t="n">
         <v>65564</v>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C7" s="6" t="n">
         <v>34711</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -41704,7 +41815,7 @@
       <c r="B8" s="2" t="n">
         <v>81785</v>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="C8" s="6" t="n">
         <v>36927</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -41725,7 +41836,7 @@
       <c r="B9" s="2" t="n">
         <v>113549</v>
       </c>
-      <c r="C9" s="4" t="n">
+      <c r="C9" s="6" t="n">
         <v>44683</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -41746,7 +41857,7 @@
       <c r="B10" s="2" t="n">
         <v>113550</v>
       </c>
-      <c r="C10" s="4" t="n">
+      <c r="C10" s="6" t="n">
         <v>44683</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -41767,7 +41878,7 @@
       <c r="B11" s="2" t="n">
         <v>113551</v>
       </c>
-      <c r="C11" s="4" t="n">
+      <c r="C11" s="6" t="n">
         <v>44683</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -41788,7 +41899,7 @@
       <c r="B12" s="2" t="n">
         <v>113552</v>
       </c>
-      <c r="C12" s="4" t="n">
+      <c r="C12" s="6" t="n">
         <v>44683</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -41809,7 +41920,7 @@
       <c r="B13" s="2" t="n">
         <v>94785</v>
       </c>
-      <c r="C13" s="4" t="n">
+      <c r="C13" s="6" t="n">
         <v>40528</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -41830,7 +41941,7 @@
       <c r="B14" s="2" t="n">
         <v>94791</v>
       </c>
-      <c r="C14" s="4" t="n">
+      <c r="C14" s="6" t="n">
         <v>40542</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -41851,7 +41962,7 @@
       <c r="B15" s="2" t="n">
         <v>94847</v>
       </c>
-      <c r="C15" s="4" t="n">
+      <c r="C15" s="6" t="n">
         <v>40556</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -41872,7 +41983,7 @@
       <c r="B16" s="2" t="n">
         <v>94855</v>
       </c>
-      <c r="C16" s="4" t="n">
+      <c r="C16" s="6" t="n">
         <v>40555</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -41893,7 +42004,7 @@
       <c r="B17" s="2" t="n">
         <v>98554</v>
       </c>
-      <c r="C17" s="4" t="n">
+      <c r="C17" s="6" t="n">
         <v>42300</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -41914,7 +42025,7 @@
       <c r="B18" s="2" t="n">
         <v>112959</v>
       </c>
-      <c r="C18" s="4" t="n">
+      <c r="C18" s="6" t="n">
         <v>45202</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
